--- a/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
+++ b/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>4.142857142857143</v>
+        <v>3.685225796097601</v>
       </c>
     </row>
     <row r="3">
@@ -416,7 +416,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>6.428571428571429</v>
+        <v>6.060529737424759</v>
       </c>
     </row>
     <row r="4">
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>13.80281690140845</v>
+        <v>13.64149449359644</v>
       </c>
     </row>
     <row r="5">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>4.886363636363637</v>
+        <v>4.826725740426121</v>
       </c>
     </row>
     <row r="6">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>7.386363636363636</v>
+        <v>7.440785791098385</v>
       </c>
     </row>
     <row r="7">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>15.30864197530864</v>
+        <v>15.00401304116144</v>
       </c>
     </row>
     <row r="8">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>2.528735632183909</v>
+        <v>2.529421979266422</v>
       </c>
     </row>
     <row r="9">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>6.32183908045977</v>
+        <v>6.404507795833029</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>12.95454545454546</v>
+        <v>13.01406999437411</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>4.204545454545455</v>
+        <v>4.253458708596975</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>6.25</v>
+        <v>6.472932673522782</v>
       </c>
     </row>
     <row r="13">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>12.7710843373494</v>
+        <v>12.91193018952538</v>
       </c>
     </row>
     <row r="14">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>2.337662337662338</v>
+        <v>2.210375012937138</v>
       </c>
     </row>
     <row r="15">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>5.584415584415584</v>
+        <v>5.501025360264888</v>
       </c>
     </row>
     <row r="16">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>10.94117647058824</v>
+        <v>11.02527052264328</v>
       </c>
     </row>
     <row r="17">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>4.047619047619047</v>
+        <v>4.12628845992028</v>
       </c>
     </row>
     <row r="18">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>7.5</v>
+        <v>7.565623878324908</v>
       </c>
     </row>
     <row r="19">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>15.1764705882353</v>
+        <v>15.28826352307805</v>
       </c>
     </row>
     <row r="20">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>2.25</v>
+        <v>2.219504648076459</v>
       </c>
     </row>
     <row r="21">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>5.25</v>
+        <v>5.211043069842796</v>
       </c>
     </row>
     <row r="22">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>10.125</v>
+        <v>10.14223888933194</v>
       </c>
     </row>
     <row r="23">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>3.170731707317073</v>
+        <v>2.892182887482616</v>
       </c>
     </row>
     <row r="24">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>6.951219512195121</v>
+        <v>6.779579213330199</v>
       </c>
     </row>
     <row r="25">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>13.90804597701149</v>
+        <v>14.0178619302433</v>
       </c>
     </row>
     <row r="26">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>3.82716049382716</v>
+        <v>3.694093999282869</v>
       </c>
     </row>
     <row r="27">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>5.80246913580247</v>
+        <v>5.656011252337658</v>
       </c>
     </row>
     <row r="28">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>14.02439024390244</v>
+        <v>14.08275416005133</v>
       </c>
     </row>
     <row r="29">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>2.027027027027027</v>
+        <v>1.797177797237573</v>
       </c>
     </row>
     <row r="30">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>4.956143444496457</v>
       </c>
     </row>
     <row r="31">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>10.75</v>
+        <v>10.70887714638119</v>
       </c>
     </row>
     <row r="32">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>3.580246913580247</v>
+        <v>3.561868363926294</v>
       </c>
     </row>
     <row r="33">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>7.407407407407407</v>
+        <v>7.52853771461441</v>
       </c>
     </row>
     <row r="34">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>15.23809523809524</v>
+        <v>15.45093079010584</v>
       </c>
     </row>
     <row r="35">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>3.291139240506329</v>
+        <v>3.197987320811357</v>
       </c>
     </row>
     <row r="36">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>5.822784810126582</v>
+        <v>5.788283550344878</v>
       </c>
     </row>
     <row r="37">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>13.75</v>
+        <v>13.79477268412488</v>
       </c>
     </row>
     <row r="38">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>3.2</v>
+        <v>3.1189948234361</v>
       </c>
     </row>
     <row r="39">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>7.066666666666667</v>
+        <v>6.797287195943042</v>
       </c>
     </row>
     <row r="40">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>14.93506493506493</v>
+        <v>14.81106481419038</v>
       </c>
     </row>
     <row r="41">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>3.25</v>
+        <v>3.296882187376386</v>
       </c>
     </row>
     <row r="42">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>6.374999999999999</v>
+        <v>6.438466832754085</v>
       </c>
     </row>
     <row r="43">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>14.14634146341463</v>
+        <v>14.15004193547107</v>
       </c>
     </row>
     <row r="44">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>8.333333333333334</v>
+        <v>8.417972576922498</v>
       </c>
     </row>
     <row r="45">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>12.67441860465116</v>
+        <v>12.68310153318386</v>
       </c>
     </row>
     <row r="46">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>24</v>
+        <v>24.37973732788076</v>
       </c>
     </row>
     <row r="47">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>21.77083333333333</v>
+        <v>21.91384999036465</v>
       </c>
     </row>
     <row r="48">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>28.95833333333334</v>
+        <v>28.94159697743767</v>
       </c>
     </row>
     <row r="49">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="D49">
-        <v>39.92874988433423</v>
+        <v>39.94830075524123</v>
       </c>
     </row>
     <row r="50">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>25.8695652173913</v>
+        <v>26.21001856477843</v>
       </c>
     </row>
     <row r="51">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>33.66666666666666</v>
+        <v>33.85572043362379</v>
       </c>
     </row>
     <row r="52">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>49.67391304347826</v>
+        <v>49.69217745657674</v>
       </c>
     </row>
     <row r="53">
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D53">
-        <v>22.44186046511628</v>
+        <v>22.60672666198426</v>
       </c>
     </row>
     <row r="54">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>31.04166666666667</v>
+        <v>31.10884899552155</v>
       </c>
     </row>
     <row r="55">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>44.6236559139785</v>
+        <v>44.35817077776242</v>
       </c>
     </row>
     <row r="56">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>18.63157894736842</v>
+        <v>18.56698965302349</v>
       </c>
     </row>
     <row r="57">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>30.36585365853659</v>
+        <v>30.35842528260586</v>
       </c>
     </row>
     <row r="58">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>44.33333333333334</v>
+        <v>44.4873693225037</v>
       </c>
     </row>
     <row r="59">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>9.651162790697676</v>
+        <v>9.678587516332962</v>
       </c>
     </row>
     <row r="60">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="D60">
-        <v>15.64705882352941</v>
+        <v>15.83424008160425</v>
       </c>
     </row>
     <row r="61">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="D61">
-        <v>30.81395348837209</v>
+        <v>30.8231525991568</v>
       </c>
     </row>
     <row r="62">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>10.48780487804878</v>
+        <v>10.39719786039766</v>
       </c>
     </row>
     <row r="63">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>16.09756097560976</v>
+        <v>16.36923957365472</v>
       </c>
     </row>
     <row r="64">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>30.77922077922078</v>
+        <v>30.73941986625719</v>
       </c>
     </row>
     <row r="65">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="D65">
-        <v>7.710843373493977</v>
+        <v>7.670525537217332</v>
       </c>
     </row>
     <row r="66">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>12.5609756097561</v>
+        <v>12.39234410302949</v>
       </c>
     </row>
     <row r="67">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D67">
-        <v>25.41176470588235</v>
+        <v>25.23604611825642</v>
       </c>
     </row>
     <row r="68">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>5.935213350388176</v>
       </c>
     </row>
     <row r="69">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>10.61728395061728</v>
+        <v>10.64745612530219</v>
       </c>
     </row>
     <row r="70">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>21.70129479072569</v>
+        <v>21.76737992939807</v>
       </c>
     </row>
     <row r="71">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="D71">
-        <v>7.5</v>
+        <v>7.481498186121565</v>
       </c>
     </row>
     <row r="72">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>13.97590361445783</v>
+        <v>14.06448569007672</v>
       </c>
     </row>
     <row r="73">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="D73">
-        <v>24.30232558139535</v>
+        <v>24.27408587935276</v>
       </c>
     </row>
     <row r="74">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D74">
-        <v>10.12820512820513</v>
+        <v>10.08005453898891</v>
       </c>
     </row>
     <row r="75">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D75">
-        <v>16.02564102564103</v>
+        <v>15.63037672488034</v>
       </c>
     </row>
     <row r="76">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D76">
-        <v>28.51351351351351</v>
+        <v>28.45559510457083</v>
       </c>
     </row>
     <row r="77">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="D77">
-        <v>5.375</v>
+        <v>5.220844808906199</v>
       </c>
     </row>
     <row r="78">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="D78">
-        <v>12.73972602739726</v>
+        <v>12.7554371644127</v>
       </c>
     </row>
     <row r="79">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D79">
-        <v>23.37349397590361</v>
+        <v>23.29944817392627</v>
       </c>
     </row>
     <row r="80">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="D80">
-        <v>7.710843373493977</v>
+        <v>7.621136303710448</v>
       </c>
     </row>
     <row r="81">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>14.43037974683544</v>
+        <v>14.26077482253129</v>
       </c>
     </row>
     <row r="82">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D82">
-        <v>27.16049382716049</v>
+        <v>27.19839229873194</v>
       </c>
     </row>
     <row r="83">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>7.635082064820283</v>
       </c>
     </row>
     <row r="84">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>16.17283950617284</v>
+        <v>16.15527563270406</v>
       </c>
     </row>
     <row r="85">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D85">
-        <v>27.71084337349398</v>
+        <v>27.95832352760834</v>
       </c>
     </row>
     <row r="86">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>8.589743589743589</v>
+        <v>8.506104894038858</v>
       </c>
     </row>
     <row r="87">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>14.60526315789474</v>
+        <v>14.61627297860222</v>
       </c>
     </row>
     <row r="88">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>27.46835443037975</v>
+        <v>27.47435658535323</v>
       </c>
     </row>
     <row r="89">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D89">
-        <v>6.410256410256411</v>
+        <v>6.211964070135982</v>
       </c>
     </row>
     <row r="90">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>15.18518518518519</v>
+        <v>15.26851188386701</v>
       </c>
     </row>
     <row r="91">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>6.625</v>
+        <v>6.508396759903823</v>
       </c>
     </row>
     <row r="93">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>12.30769230769231</v>
+        <v>12.2243276496713</v>
       </c>
     </row>
     <row r="94">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="D94">
-        <v>25.69620253164557</v>
+        <v>25.66383801622998</v>
       </c>
     </row>
     <row r="95">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>6.8</v>
+        <v>6.59279647462121</v>
       </c>
     </row>
     <row r="96">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>12.66666666666667</v>
+        <v>12.92235967052276</v>
       </c>
     </row>
     <row r="97">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="D97">
-        <v>23.95061728395062</v>
+        <v>24.0620392036849</v>
       </c>
     </row>
     <row r="98">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>7.195121951219512</v>
+        <v>7.212142414435846</v>
       </c>
     </row>
     <row r="99">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>13.85542168674699</v>
+        <v>14.05714747071492</v>
       </c>
     </row>
     <row r="100">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>26.3855421686747</v>
+        <v>26.34056294165304</v>
       </c>
     </row>
     <row r="101">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>5.753424657534246</v>
+        <v>5.562336860887401</v>
       </c>
     </row>
     <row r="102">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>12.7027027027027</v>
+        <v>12.7404360940069</v>
       </c>
     </row>
     <row r="103">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>24.05063291139241</v>
+        <v>24.11894977410222</v>
       </c>
     </row>
     <row r="104">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>4.558823529411764</v>
+        <v>4.4505570333358</v>
       </c>
     </row>
     <row r="105">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>10.88235294117647</v>
+        <v>10.84171340267484</v>
       </c>
     </row>
     <row r="106">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>23.78787878787879</v>
+        <v>23.70939925705494</v>
       </c>
     </row>
     <row r="107">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>3.970588235294117</v>
+        <v>3.914209112377542</v>
       </c>
     </row>
     <row r="108">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>12.34375</v>
+        <v>12.56316505105122</v>
       </c>
     </row>
     <row r="109">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="D109">
-        <v>25</v>
+        <v>24.59173645562257</v>
       </c>
     </row>
     <row r="110">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="D110">
-        <v>5.411764705882353</v>
+        <v>5.442074269681893</v>
       </c>
     </row>
     <row r="111">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="D111">
-        <v>11.68674698795181</v>
+        <v>11.78432108213274</v>
       </c>
     </row>
     <row r="112">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="D112">
-        <v>22.26047045324154</v>
+        <v>22.07518110409443</v>
       </c>
     </row>
     <row r="113">
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>6.046511627906976</v>
+        <v>6.000051135671056</v>
       </c>
     </row>
     <row r="114">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="D114">
-        <v>12.32558139534884</v>
+        <v>12.22175816757322</v>
       </c>
     </row>
     <row r="115">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>22.61904761904762</v>
+        <v>22.54580681875276</v>
       </c>
     </row>
     <row r="116">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="D116">
-        <v>5.164835164835166</v>
+        <v>5.194685383569787</v>
       </c>
     </row>
     <row r="117">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="D117">
-        <v>10.86021505376344</v>
+        <v>10.81592954097202</v>
       </c>
     </row>
     <row r="118">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>18.49009620826259</v>
+        <v>18.40023947363986</v>
       </c>
     </row>
     <row r="119">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>6.385542168674698</v>
+        <v>6.544160786273939</v>
       </c>
     </row>
     <row r="120">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>12.5974025974026</v>
+        <v>12.68195461690708</v>
       </c>
     </row>
     <row r="121">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>24.125</v>
+        <v>24.08549959927849</v>
       </c>
     </row>
     <row r="122">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="D122">
-        <v>4.268292682926829</v>
+        <v>4.435287148353349</v>
       </c>
     </row>
     <row r="123">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>10.68965517241379</v>
+        <v>10.70521359610122</v>
       </c>
     </row>
     <row r="124">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>18.43511978950284</v>
+        <v>18.44215184083298</v>
       </c>
     </row>
     <row r="125">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>5.952380952380953</v>
+        <v>6.167223672436083</v>
       </c>
     </row>
     <row r="126">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>11.75</v>
+        <v>11.9186273534628</v>
       </c>
     </row>
     <row r="127">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>24.50549450549451</v>
+        <v>24.3820733214387</v>
       </c>
     </row>
     <row r="128">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>4.941176470588236</v>
+        <v>4.932219098141676</v>
       </c>
     </row>
     <row r="129">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>12.93333333333333</v>
+        <v>13.00259698603256</v>
       </c>
     </row>
     <row r="130">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>25.41176470588235</v>
+        <v>25.51456146898484</v>
       </c>
     </row>
     <row r="131">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>4.269662921348314</v>
+        <v>4.27488820331469</v>
       </c>
     </row>
     <row r="132">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>11.44444444444444</v>
+        <v>11.43356520489169</v>
       </c>
     </row>
     <row r="133">
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>23.76470588235294</v>
+        <v>23.90781847576718</v>
       </c>
     </row>
     <row r="134">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>5.168438537360801</v>
       </c>
     </row>
     <row r="135">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>12.65060240963856</v>
+        <v>12.66754208559282</v>
       </c>
     </row>
     <row r="136">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>25.22727272727273</v>
+        <v>25.06150221709633</v>
       </c>
     </row>
     <row r="137">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>5.061728395061729</v>
+        <v>4.823066970640868</v>
       </c>
     </row>
     <row r="138">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>14.15584415584416</v>
+        <v>14.17552334534968</v>
       </c>
     </row>
     <row r="139">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>25.24390243902439</v>
+        <v>25.4105207386475</v>
       </c>
     </row>
     <row r="140">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>4.186046511627907</v>
+        <v>4.101931755908767</v>
       </c>
     </row>
     <row r="141">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="D141">
-        <v>13.11111111111111</v>
+        <v>13.01314595386709</v>
       </c>
     </row>
     <row r="142">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>23.17647058823529</v>
+        <v>23.19242888079821</v>
       </c>
     </row>
     <row r="143">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>5.875</v>
+        <v>5.911894788510364</v>
       </c>
     </row>
     <row r="144">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>11.53846153846154</v>
+        <v>11.39467215673453</v>
       </c>
     </row>
     <row r="145">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>23.38235294117647</v>
+        <v>23.54835399245625</v>
       </c>
     </row>
     <row r="146">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="D146">
-        <v>7.323943661971832</v>
+        <v>7.402823554492952</v>
       </c>
     </row>
     <row r="147">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D147">
-        <v>14.42857142857143</v>
+        <v>14.4220334898657</v>
       </c>
     </row>
     <row r="148">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="D148">
-        <v>28.91891891891892</v>
+        <v>29.08352316560843</v>
       </c>
     </row>
     <row r="149">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="D149">
-        <v>6.049382716049383</v>
+        <v>5.708150486197449</v>
       </c>
     </row>
     <row r="150">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>13.0379746835443</v>
+        <v>12.91183754948726</v>
       </c>
     </row>
     <row r="151">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="D151">
-        <v>25.40229885057471</v>
+        <v>25.46678957242804</v>
       </c>
     </row>
     <row r="152">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>5.97560975609756</v>
+        <v>6.131851379798523</v>
       </c>
     </row>
     <row r="153">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>12.2093023255814</v>
+        <v>12.10609146102434</v>
       </c>
     </row>
     <row r="154">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>24.69879518072289</v>
+        <v>24.69509320135116</v>
       </c>
     </row>
     <row r="155">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>4.583333333333333</v>
+        <v>4.681240774353519</v>
       </c>
     </row>
     <row r="156">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>10.58823529411765</v>
+        <v>10.49899476091725</v>
       </c>
     </row>
     <row r="157">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>17.57843137254902</v>
+        <v>17.64481398657003</v>
       </c>
     </row>
     <row r="158">
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>4.938271604938271</v>
+        <v>4.998216388852796</v>
       </c>
     </row>
     <row r="159">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>8.888888888888889</v>
+        <v>8.992975962398614</v>
       </c>
     </row>
     <row r="160">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>17.12328767123288</v>
+        <v>16.91299089986073</v>
       </c>
     </row>
     <row r="161">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>4.324324324324325</v>
+        <v>4.710195275975137</v>
       </c>
     </row>
     <row r="162">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>7.837837837837837</v>
+        <v>8.235936051110492</v>
       </c>
     </row>
     <row r="163">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>13.47222222222222</v>
+        <v>13.2411302449259</v>
       </c>
     </row>
     <row r="164">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="D164">
-        <v>5.211267605633802</v>
+        <v>5.235526350957272</v>
       </c>
     </row>
     <row r="165">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="D165">
-        <v>9.014084507042254</v>
+        <v>8.949504834993757</v>
       </c>
     </row>
     <row r="166">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="D166">
-        <v>16.4</v>
+        <v>16.10784446595772</v>
       </c>
     </row>
     <row r="167">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="D167">
-        <v>3.291139240506329</v>
+        <v>3.196380130816514</v>
       </c>
     </row>
     <row r="168">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>7.974683544303798</v>
+        <v>7.947668778371127</v>
       </c>
     </row>
     <row r="169">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>15.20547945205479</v>
+        <v>15.46346144337112</v>
       </c>
     </row>
     <row r="170">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>3.943661971830986</v>
+        <v>4.022532286561306</v>
       </c>
     </row>
     <row r="171">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>7.887323943661971</v>
+        <v>7.869762218194597</v>
       </c>
     </row>
     <row r="172">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>14.52054794520548</v>
+        <v>14.72445759196292</v>
       </c>
     </row>
     <row r="173">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>3.636363636363637</v>
+        <v>3.49482901715474</v>
       </c>
     </row>
     <row r="174">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>7.272727272727273</v>
+        <v>7.282801826068171</v>
       </c>
     </row>
     <row r="175">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>14.25</v>
+        <v>14.23668866607781</v>
       </c>
     </row>
     <row r="176">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>3.287671232876712</v>
+        <v>3.325225000049993</v>
       </c>
     </row>
     <row r="177">
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>6.575342465753424</v>
+        <v>6.486997236306701</v>
       </c>
     </row>
     <row r="178">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>15.78947368421053</v>
+        <v>15.40366242584833</v>
       </c>
     </row>
     <row r="179">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>2.933333333333333</v>
+        <v>2.791974590910961</v>
       </c>
     </row>
     <row r="180">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>6.533333333333333</v>
+        <v>6.545013357952921</v>
       </c>
     </row>
     <row r="181">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>13.50649350649351</v>
+        <v>13.61850834705933</v>
       </c>
     </row>
     <row r="182">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>6.268656716417911</v>
+        <v>5.910744964276597</v>
       </c>
     </row>
     <row r="183">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>10.46875</v>
+        <v>10.42089156632262</v>
       </c>
     </row>
     <row r="184">
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>19.12243150684931</v>
+        <v>19.05618097858698</v>
       </c>
     </row>
     <row r="185">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>6.119402985074627</v>
+        <v>6.156304370977379</v>
       </c>
     </row>
     <row r="186">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>10.26315789473684</v>
+        <v>10.21727871051709</v>
       </c>
     </row>
     <row r="187">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>16.05263157894737</v>
+        <v>16.36543205786478</v>
       </c>
     </row>
     <row r="188">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>3.582089552238806</v>
+        <v>3.741934778295222</v>
       </c>
     </row>
     <row r="189">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>6.716417910447761</v>
+        <v>6.861050172925603</v>
       </c>
     </row>
     <row r="190">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>13.42465753424658</v>
+        <v>13.50810431690086</v>
       </c>
     </row>
     <row r="191">
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>5.416666666666666</v>
+        <v>5.588578148195052</v>
       </c>
     </row>
     <row r="192">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>9.583333333333334</v>
+        <v>9.497517174436883</v>
       </c>
     </row>
     <row r="193">
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>18.83547008547009</v>
+        <v>18.82349772330201</v>
       </c>
     </row>
     <row r="194">
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="D194">
-        <v>4.788732394366197</v>
+        <v>4.794821373123635</v>
       </c>
     </row>
     <row r="195">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D195">
-        <v>7.183098591549296</v>
+        <v>6.96552905058366</v>
       </c>
     </row>
     <row r="196">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>14.1025641025641</v>
+        <v>14.17243172900661</v>
       </c>
     </row>
     <row r="197">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="D197">
-        <v>10.72727272727273</v>
+        <v>10.75191004176526</v>
       </c>
     </row>
     <row r="198">
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="D198">
-        <v>16.72727272727273</v>
+        <v>16.13736228032284</v>
       </c>
     </row>
     <row r="199">
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D199">
-        <v>30.52631578947368</v>
+        <v>30.29888299102025</v>
       </c>
     </row>
     <row r="200">
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="D200">
-        <v>26.82352941176471</v>
+        <v>26.99287021510981</v>
       </c>
     </row>
     <row r="201">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="D201">
-        <v>36.5</v>
+        <v>36.63228126920093</v>
       </c>
     </row>
     <row r="202">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="D202">
-        <v>49.74683544303797</v>
+        <v>49.64962897103564</v>
       </c>
     </row>
     <row r="203">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="D203">
-        <v>29.18918918918919</v>
+        <v>28.87353673562908</v>
       </c>
     </row>
     <row r="204">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="D204">
-        <v>38.13333333333333</v>
+        <v>38.19373089771111</v>
       </c>
     </row>
     <row r="205">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>51.23456790123457</v>
+        <v>51.35785511064351</v>
       </c>
     </row>
     <row r="206">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>23.47826086956522</v>
+        <v>23.22657136684287</v>
       </c>
     </row>
     <row r="207">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="D207">
-        <v>31.97183098591549</v>
+        <v>31.93209007869573</v>
       </c>
     </row>
     <row r="208">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="D208">
-        <v>46.76470588235294</v>
+        <v>47.07416008101185</v>
       </c>
     </row>
     <row r="209">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="D209">
-        <v>22.24137931034483</v>
+        <v>22.46118574564798</v>
       </c>
     </row>
     <row r="210">
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="D210">
-        <v>32.3943661971831</v>
+        <v>32.1511019488425</v>
       </c>
     </row>
     <row r="211">
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="D211">
-        <v>44.57142857142857</v>
+        <v>44.67031621245329</v>
       </c>
     </row>
     <row r="212">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="D212">
-        <v>12.43243243243243</v>
+        <v>12.51936666560602</v>
       </c>
     </row>
     <row r="213">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="D213">
-        <v>19.18207681365576</v>
+        <v>19.20141585249397</v>
       </c>
     </row>
     <row r="214">
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D214">
-        <v>31.21621621621622</v>
+        <v>31.12543076533419</v>
       </c>
     </row>
     <row r="215">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="D215">
-        <v>7.662337662337663</v>
+        <v>7.398399087871278</v>
       </c>
     </row>
     <row r="216">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D216">
-        <v>14.70588235294118</v>
+        <v>14.73390433792328</v>
       </c>
     </row>
     <row r="217">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="D217">
-        <v>28.16901408450704</v>
+        <v>28.273174701977</v>
       </c>
     </row>
     <row r="218">
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>7.65432098765432</v>
+        <v>7.669408975312855</v>
       </c>
     </row>
     <row r="219">
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="D219">
-        <v>14.66666666666667</v>
+        <v>14.76466615963838</v>
       </c>
     </row>
     <row r="220">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>26.25</v>
+        <v>26.28341171869635</v>
       </c>
     </row>
     <row r="221">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="D221">
-        <v>6.666666666666666</v>
+        <v>6.524543409419688</v>
       </c>
     </row>
     <row r="222">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>11.46666666666667</v>
+        <v>11.47174402640319</v>
       </c>
     </row>
     <row r="223">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>24.80519480519481</v>
+        <v>25.05885768223203</v>
       </c>
     </row>
     <row r="224">
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>6.470588235294118</v>
+        <v>6.298370128966183</v>
       </c>
     </row>
     <row r="225">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>11.88405797101449</v>
+        <v>11.95383968314153</v>
       </c>
     </row>
     <row r="226">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>23.33333333333333</v>
+        <v>23.59421550099251</v>
       </c>
     </row>
     <row r="227">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="D227">
-        <v>7.5</v>
+        <v>7.509042630898817</v>
       </c>
     </row>
     <row r="228">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>12.57575757575758</v>
+        <v>12.75839874800015</v>
       </c>
     </row>
     <row r="229">
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="D229">
-        <v>26.02739726027397</v>
+        <v>25.98648760649906</v>
       </c>
     </row>
     <row r="230">
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D230">
-        <v>7.162162162162163</v>
+        <v>7.437866721185186</v>
       </c>
     </row>
     <row r="231">
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="D231">
-        <v>12.17391304347826</v>
+        <v>12.29688385478446</v>
       </c>
     </row>
     <row r="232">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="D232">
-        <v>24.66666666666667</v>
+        <v>24.68463435658308</v>
       </c>
     </row>
     <row r="233">
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>5.270270270270269</v>
+        <v>5.091795183289094</v>
       </c>
     </row>
     <row r="234">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>10.27777777777778</v>
+        <v>10.27813742634264</v>
       </c>
     </row>
     <row r="235">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>20.74561403508772</v>
+        <v>20.80877283752077</v>
       </c>
     </row>
     <row r="236">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>8.714285714285714</v>
+        <v>8.761263547790453</v>
       </c>
     </row>
     <row r="237">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>15.73529411764706</v>
+        <v>15.93943892205238</v>
       </c>
     </row>
     <row r="238">
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="D238">
-        <v>29.72602739726027</v>
+        <v>29.71661667942666</v>
       </c>
     </row>
     <row r="239">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="D239">
-        <v>9.863013698630137</v>
+        <v>9.852095188357314</v>
       </c>
     </row>
     <row r="240">
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>19.22009669960059</v>
+        <v>19.29812718502892</v>
       </c>
     </row>
     <row r="241">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D241">
-        <v>34</v>
+        <v>34.12378122989298</v>
       </c>
     </row>
     <row r="242">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D242">
-        <v>10.3125</v>
+        <v>10.38681001141584</v>
       </c>
     </row>
     <row r="243">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="D243">
-        <v>17.1875</v>
+        <v>17.33301201115656</v>
       </c>
     </row>
     <row r="244">
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="D244">
-        <v>28.71428571428572</v>
+        <v>28.82460723966872</v>
       </c>
     </row>
     <row r="245">
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D245">
-        <v>6.176470588235294</v>
+        <v>6.2250701788204</v>
       </c>
     </row>
     <row r="246">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="D246">
-        <v>12.79411764705882</v>
+        <v>12.7488034454403</v>
       </c>
     </row>
     <row r="247">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>25.55555555555556</v>
+        <v>25.17275951157797</v>
       </c>
     </row>
     <row r="248">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="D248">
-        <v>5.161290322580645</v>
+        <v>4.870339811481849</v>
       </c>
     </row>
     <row r="249">
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>11.80327868852459</v>
+        <v>11.86231183874567</v>
       </c>
     </row>
     <row r="250">
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="D250">
-        <v>23.28358208955224</v>
+        <v>23.59252762714859</v>
       </c>
     </row>
     <row r="251">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="D251">
-        <v>4.626865671641791</v>
+        <v>4.692932006581518</v>
       </c>
     </row>
     <row r="252">
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="D252">
-        <v>10.8695652173913</v>
+        <v>10.87534677620336</v>
       </c>
     </row>
     <row r="253">
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="D253">
-        <v>22.89855072463768</v>
+        <v>22.96845744140189</v>
       </c>
     </row>
     <row r="254">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="D254">
-        <v>5.82089552238806</v>
+        <v>5.750330029007619</v>
       </c>
     </row>
     <row r="255">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>13.6231884057971</v>
+        <v>13.39216337198151</v>
       </c>
     </row>
     <row r="256">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>25.57142857142857</v>
+        <v>25.57975540008733</v>
       </c>
     </row>
     <row r="257">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D257">
-        <v>4.6875</v>
+        <v>4.554715414664873</v>
       </c>
     </row>
     <row r="258">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D258">
-        <v>12.03125</v>
+        <v>12.01721950947282</v>
       </c>
     </row>
     <row r="259">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="D259">
-        <v>25</v>
+        <v>25.40609176315192</v>
       </c>
     </row>
     <row r="260">
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="D260">
-        <v>4.098360655737705</v>
+        <v>4.052687448111717</v>
       </c>
     </row>
     <row r="261">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D261">
-        <v>11.31147540983607</v>
+        <v>11.55527915565783</v>
       </c>
     </row>
     <row r="262">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D262">
-        <v>22.61538461538462</v>
+        <v>22.53085488146424</v>
       </c>
     </row>
     <row r="263">
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="D263">
-        <v>6.555555555555555</v>
+        <v>6.631495269336487</v>
       </c>
     </row>
     <row r="264">
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="D264">
-        <v>15.77777777777778</v>
+        <v>15.80951272965379</v>
       </c>
     </row>
     <row r="265">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D265">
-        <v>26.76470588235294</v>
+        <v>26.67158202877681</v>
       </c>
     </row>
     <row r="266">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D266">
-        <v>5.842696629213483</v>
+        <v>5.349214410339786</v>
       </c>
     </row>
     <row r="267">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="D267">
-        <v>14.66666666666667</v>
+        <v>14.62757879511282</v>
       </c>
     </row>
     <row r="268">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="D268">
-        <v>25.65656565656566</v>
+        <v>25.89245680910768</v>
       </c>
     </row>
     <row r="269">
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="D269">
-        <v>4.186046511627907</v>
+        <v>4.206235538194951</v>
       </c>
     </row>
     <row r="270">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D270">
-        <v>12.06896551724138</v>
+        <v>12.0618334226017</v>
       </c>
     </row>
     <row r="271">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D271">
-        <v>24.5631067961165</v>
+        <v>24.74337155321622</v>
       </c>
     </row>
     <row r="272">
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="D272">
-        <v>3.829787234042553</v>
+        <v>3.709355861878632</v>
       </c>
     </row>
     <row r="273">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="D274">
-        <v>21.82129742962056</v>
+        <v>21.8791295432245</v>
       </c>
     </row>
     <row r="275">
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D275">
-        <v>5.842696629213483</v>
+        <v>6.345464025894161</v>
       </c>
     </row>
     <row r="276">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D276">
-        <v>12.62626262626263</v>
+        <v>12.39391008263184</v>
       </c>
     </row>
     <row r="277">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="D277">
-        <v>23.89473684210526</v>
+        <v>23.49786130959714</v>
       </c>
     </row>
     <row r="278">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="D278">
-        <v>4.712643678160919</v>
+        <v>4.878418981092032</v>
       </c>
     </row>
     <row r="279">
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="D279">
-        <v>13.26732673267327</v>
+        <v>13.42662363267418</v>
       </c>
     </row>
     <row r="280">
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="D280">
-        <v>26.37254901960784</v>
+        <v>26.63842203846296</v>
       </c>
     </row>
     <row r="281">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="D281">
-        <v>5.853658536585366</v>
+        <v>5.384383297946298</v>
       </c>
     </row>
     <row r="282">
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>14.74358974358974</v>
+        <v>14.70783525380426</v>
       </c>
     </row>
     <row r="283">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="D283">
-        <v>25.89285714285714</v>
+        <v>26.03741143059548</v>
       </c>
     </row>
     <row r="284">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D284">
-        <v>4.777777777777778</v>
+        <v>4.683728334505173</v>
       </c>
     </row>
     <row r="285">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>13.47826086956522</v>
+        <v>13.47970289847173</v>
       </c>
     </row>
     <row r="286">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="D286">
-        <v>25.48387096774194</v>
+        <v>25.75165670000204</v>
       </c>
     </row>
     <row r="287">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="D287">
-        <v>5.977011494252874</v>
+        <v>5.414723938960424</v>
       </c>
     </row>
     <row r="288">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="D288">
-        <v>14.35294117647059</v>
+        <v>13.99874069065162</v>
       </c>
     </row>
     <row r="289">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D289">
-        <v>26.16279069767442</v>
+        <v>26.63663052448497</v>
       </c>
     </row>
     <row r="290">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="D290">
-        <v>4.827586206896552</v>
+        <v>4.516270678962129</v>
       </c>
     </row>
     <row r="291">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="D291">
-        <v>11.17647058823529</v>
+        <v>11.31250897362911</v>
       </c>
     </row>
     <row r="292">
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="D292">
-        <v>21.84218077474893</v>
+        <v>21.89119592618533</v>
       </c>
     </row>
     <row r="293">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="D293">
-        <v>5.930232558139535</v>
+        <v>5.420596950183324</v>
       </c>
     </row>
     <row r="294">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="D294">
-        <v>13.92405063291139</v>
+        <v>13.78237899001062</v>
       </c>
     </row>
     <row r="295">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D295">
-        <v>28.31168831168831</v>
+        <v>28.12282628257245</v>
       </c>
     </row>
     <row r="296">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="D296">
-        <v>5.980392156862745</v>
+        <v>6.101883046427322</v>
       </c>
     </row>
     <row r="297">
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="D297">
-        <v>14.16666666666667</v>
+        <v>14.46429996756167</v>
       </c>
     </row>
     <row r="298">
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="D298">
-        <v>25.8695652173913</v>
+        <v>25.91758966708806</v>
       </c>
     </row>
     <row r="299">
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="D299">
-        <v>8.023255813953488</v>
+        <v>7.83871394270524</v>
       </c>
     </row>
     <row r="300">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="D300">
-        <v>18.26430722891566</v>
+        <v>18.25116173820857</v>
       </c>
     </row>
     <row r="301">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="D301">
-        <v>29.0625</v>
+        <v>29.21485334505552</v>
       </c>
     </row>
     <row r="302">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="D302">
-        <v>6.162790697674419</v>
+        <v>6.014338832325178</v>
       </c>
     </row>
     <row r="303">
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="D303">
-        <v>17.02380952380952</v>
+        <v>16.82365063925133</v>
       </c>
     </row>
     <row r="304">
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="D304">
-        <v>31.12244897959184</v>
+        <v>31.02424420233584</v>
       </c>
     </row>
     <row r="305">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D305">
-        <v>8.378378378378379</v>
+        <v>8.219005805999657</v>
       </c>
     </row>
     <row r="306">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="D306">
-        <v>20.18087855297158</v>
+        <v>19.66228489123335</v>
       </c>
     </row>
     <row r="307">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="D307">
-        <v>33.56435643564356</v>
+        <v>33.36730743687373</v>
       </c>
     </row>
     <row r="308">
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="D308">
-        <v>3.763440860215054</v>
+        <v>3.6349493549969</v>
       </c>
     </row>
     <row r="309">
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="D309">
-        <v>10.10526315789474</v>
+        <v>10.11050115125111</v>
       </c>
     </row>
     <row r="310">
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D310">
-        <v>16.63157894736842</v>
+        <v>16.42017499049537</v>
       </c>
     </row>
     <row r="311">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="D311">
-        <v>4.188034188034188</v>
+        <v>3.977230540665857</v>
       </c>
     </row>
     <row r="312">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="D312">
-        <v>8.205128205128204</v>
+        <v>8.238228207578885</v>
       </c>
     </row>
     <row r="313">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="D313">
-        <v>15.32110091743119</v>
+        <v>15.42942871566926</v>
       </c>
     </row>
     <row r="314">
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="D314">
-        <v>3.398058252427185</v>
+        <v>3.425208838612741</v>
       </c>
     </row>
     <row r="315">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D315">
-        <v>7.961165048543689</v>
+        <v>8.026509093648716</v>
       </c>
     </row>
     <row r="316">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="D316">
-        <v>13.94230769230769</v>
+        <v>13.83632104810355</v>
       </c>
     </row>
     <row r="317">
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="D317">
-        <v>3.191489361702128</v>
+        <v>3.218378908891774</v>
       </c>
     </row>
     <row r="318">
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="D318">
-        <v>7.659574468085107</v>
+        <v>7.866500759283099</v>
       </c>
     </row>
     <row r="319">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="D319">
-        <v>13.39805825242718</v>
+        <v>13.23195813812105</v>
       </c>
     </row>
     <row r="320">
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="D320">
-        <v>3.809523809523809</v>
+        <v>3.766302624944184</v>
       </c>
     </row>
     <row r="321">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="D321">
-        <v>7.80952380952381</v>
+        <v>7.634820589984834</v>
       </c>
     </row>
     <row r="322">
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="D322">
-        <v>13.67924528301887</v>
+        <v>14.04745597323936</v>
       </c>
     </row>
     <row r="323">
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="D323">
-        <v>3.513513513513514</v>
+        <v>3.458306529438883</v>
       </c>
     </row>
     <row r="324">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="D324">
-        <v>6.846846846846847</v>
+        <v>6.710999456412623</v>
       </c>
     </row>
     <row r="325">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="D325">
-        <v>12.47619047619048</v>
+        <v>12.28850060630379</v>
       </c>
     </row>
     <row r="326">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="D326">
-        <v>3.333333333333333</v>
+        <v>3.128694008579072</v>
       </c>
     </row>
     <row r="327">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="D327">
-        <v>7.111111111111112</v>
+        <v>7.225202870356553</v>
       </c>
     </row>
     <row r="328">
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="D328">
-        <v>12.4468085106383</v>
+        <v>12.82281884062744</v>
       </c>
     </row>
     <row r="329">
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="D329">
-        <v>3.523809523809524</v>
+        <v>3.536389176905308</v>
       </c>
     </row>
     <row r="330">
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="D330">
-        <v>7.047619047619048</v>
+        <v>7.064997935219369</v>
       </c>
     </row>
     <row r="331">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="D331">
-        <v>11.26126126126126</v>
+        <v>11.19374909605078</v>
       </c>
     </row>
     <row r="332">
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="D332">
-        <v>3.564356435643564</v>
+        <v>3.517101731044673</v>
       </c>
     </row>
     <row r="333">
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="D333">
-        <v>7.623762376237624</v>
+        <v>7.450481302466693</v>
       </c>
     </row>
     <row r="334">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="D334">
-        <v>13.7037037037037</v>
+        <v>13.70987075558255</v>
       </c>
     </row>
     <row r="335">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D335">
-        <v>2.6</v>
+        <v>2.44455895400372</v>
       </c>
     </row>
     <row r="336">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="D336">
-        <v>5.500000000000001</v>
+        <v>5.216849297711635</v>
       </c>
     </row>
     <row r="337">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="D337">
-        <v>11.17021276595745</v>
+        <v>11.40182503458006</v>
       </c>
     </row>
     <row r="338">
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="D338">
-        <v>2.621359223300971</v>
+        <v>2.531755231569268</v>
       </c>
     </row>
     <row r="339">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="D339">
-        <v>5.631067961165049</v>
+        <v>5.541244937880761</v>
       </c>
     </row>
     <row r="340">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="D340">
-        <v>11.60377358490566</v>
+        <v>11.67915398099378</v>
       </c>
     </row>
     <row r="341">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="D341">
-        <v>4.059405940594059</v>
+        <v>4.03390565677894</v>
       </c>
     </row>
     <row r="342">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="D342">
-        <v>7.128712871287128</v>
+        <v>7.082203851823957</v>
       </c>
     </row>
     <row r="343">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="D343">
-        <v>14.1747572815534</v>
+        <v>14.33674175848242</v>
       </c>
     </row>
     <row r="344">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="D344">
-        <v>2.647058823529412</v>
+        <v>2.81015544718536</v>
       </c>
     </row>
     <row r="345">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D345">
-        <v>5.588235294117647</v>
+        <v>5.574891248144008</v>
       </c>
     </row>
     <row r="346">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="D346">
-        <v>10.19607843137255</v>
+        <v>10.21530757732704</v>
       </c>
     </row>
     <row r="347">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="D347">
-        <v>4.329896907216495</v>
+        <v>4.165757989575734</v>
       </c>
     </row>
     <row r="348">
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="D348">
-        <v>8.041237113402062</v>
+        <v>8.211029338959245</v>
       </c>
     </row>
     <row r="349">
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="D349">
-        <v>13.75</v>
+        <v>13.67698510560965</v>
       </c>
     </row>
     <row r="350">
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="D350">
-        <v>8.085106382978722</v>
+        <v>8.007656954473042</v>
       </c>
     </row>
     <row r="351">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="D351">
-        <v>12.84313725490196</v>
+        <v>13.2793373091607</v>
       </c>
     </row>
     <row r="352">
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="D352">
-        <v>18.90196078431373</v>
+        <v>19.0099697292832</v>
       </c>
     </row>
     <row r="353">
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="D353">
-        <v>14.02439024390244</v>
+        <v>14.65089536566943</v>
       </c>
     </row>
     <row r="354">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="D354">
-        <v>23.18681318681319</v>
+        <v>22.85772977244308</v>
       </c>
     </row>
     <row r="355">
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="D355">
-        <v>34.83870967741935</v>
+        <v>34.64756870116229</v>
       </c>
     </row>
     <row r="356">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="D356">
-        <v>18.52631578947368</v>
+        <v>18.65634538780538</v>
       </c>
     </row>
     <row r="357">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="D357">
-        <v>28.17204301075269</v>
+        <v>27.84260654062342</v>
       </c>
     </row>
     <row r="358">
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="D358">
-        <v>39.03225806451613</v>
+        <v>38.93451674663208</v>
       </c>
     </row>
     <row r="359">
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="D359">
-        <v>16.95238095238095</v>
+        <v>16.77730646300213</v>
       </c>
     </row>
     <row r="360">
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="D360">
-        <v>27.06422018348624</v>
+        <v>27.04594074295498</v>
       </c>
     </row>
     <row r="361">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="D361">
-        <v>37.70642201834863</v>
+        <v>37.3933252883466</v>
       </c>
     </row>
     <row r="362">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="D362">
-        <v>15.1</v>
+        <v>14.69866124001517</v>
       </c>
     </row>
     <row r="363">
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="D363">
-        <v>23.61904761904762</v>
+        <v>23.6845758843451</v>
       </c>
     </row>
     <row r="364">
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="D364">
-        <v>34.43396226415094</v>
+        <v>34.79729326724932</v>
       </c>
     </row>
     <row r="365">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="D365">
-        <v>10.2803738317757</v>
+        <v>10.28042905307037</v>
       </c>
     </row>
     <row r="366">
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="D366">
-        <v>17.66355140186916</v>
+        <v>17.70557193198582</v>
       </c>
     </row>
     <row r="367">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="D367">
-        <v>29</v>
+        <v>29.00573638579855</v>
       </c>
     </row>
     <row r="368">
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="D368">
-        <v>6.422018348623854</v>
+        <v>6.474743825349387</v>
       </c>
     </row>
     <row r="369">
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="D369">
-        <v>12.80373831775701</v>
+        <v>12.96943714885955</v>
       </c>
     </row>
     <row r="370">
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="D370">
-        <v>21.72496662216288</v>
+        <v>21.69657673954115</v>
       </c>
     </row>
     <row r="371">
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="D371">
-        <v>4.845360824742268</v>
+        <v>4.873547040611218</v>
       </c>
     </row>
     <row r="372">
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="D372">
-        <v>12.31578947368421</v>
+        <v>12.16941138926549</v>
       </c>
     </row>
     <row r="373">
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="D373">
-        <v>19.14210526315789</v>
+        <v>19.29075592179443</v>
       </c>
     </row>
     <row r="374">
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="D374">
-        <v>5.294117647058824</v>
+        <v>5.441884722788836</v>
       </c>
     </row>
     <row r="375">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="D375">
-        <v>9.117647058823529</v>
+        <v>9.104773457233595</v>
       </c>
     </row>
     <row r="376">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="D376">
-        <v>15.76923076923077</v>
+        <v>15.9021934692295</v>
       </c>
     </row>
     <row r="377">
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="D377">
-        <v>4.901960784313725</v>
+        <v>4.891092955640294</v>
       </c>
     </row>
     <row r="378">
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="D378">
-        <v>9.607843137254902</v>
+        <v>9.49889785581524</v>
       </c>
     </row>
     <row r="379">
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="D379">
-        <v>17.28155339805825</v>
+        <v>17.26907863181795</v>
       </c>
     </row>
     <row r="380">
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="D380">
-        <v>3.928571428571428</v>
+        <v>4.060228742985249</v>
       </c>
     </row>
     <row r="381">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="D381">
-        <v>7.976190476190477</v>
+        <v>8.065244700482808</v>
       </c>
     </row>
     <row r="382">
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="D382">
-        <v>15</v>
+        <v>14.9895167138187</v>
       </c>
     </row>
     <row r="383">
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="D383">
-        <v>5.048543689320388</v>
+        <v>5.0560363568682</v>
       </c>
     </row>
     <row r="384">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="D384">
-        <v>9.902912621359224</v>
+        <v>9.897395297632837</v>
       </c>
     </row>
     <row r="385">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="D385">
-        <v>17.28971962616822</v>
+        <v>17.23437859675177</v>
       </c>
     </row>
     <row r="386">
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="D386">
-        <v>5.392156862745098</v>
+        <v>4.908885571956795</v>
       </c>
     </row>
     <row r="387">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D387">
-        <v>10.22988505747126</v>
+        <v>10.218110263254</v>
       </c>
     </row>
     <row r="388">
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="D388">
-        <v>18.86799024730059</v>
+        <v>19.37799477581197</v>
       </c>
     </row>
     <row r="389">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="D389">
-        <v>5.555555555555555</v>
+        <v>5.334342549822301</v>
       </c>
     </row>
     <row r="390">
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="D390">
-        <v>10.91836734693878</v>
+        <v>10.89919049570149</v>
       </c>
     </row>
     <row r="391">
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="D391">
-        <v>19.66659931299252</v>
+        <v>19.79869175425435</v>
       </c>
     </row>
     <row r="392">
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="D392">
-        <v>4.375</v>
+        <v>4.178900386103525</v>
       </c>
     </row>
     <row r="393">
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="D393">
-        <v>10.3960396039604</v>
+        <v>10.41835668210043</v>
       </c>
     </row>
     <row r="394">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="D394">
-        <v>20.2503269194844</v>
+        <v>20.16504418724712</v>
       </c>
     </row>
     <row r="395">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="D395">
-        <v>4.666666666666666</v>
+        <v>4.640628111311345</v>
       </c>
     </row>
     <row r="396">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="D396">
-        <v>12.01923076923077</v>
+        <v>12.02640346854916</v>
       </c>
     </row>
     <row r="397">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="D397">
-        <v>22.56880733944954</v>
+        <v>22.61948089960124</v>
       </c>
     </row>
     <row r="398">
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="D398">
-        <v>3.595505617977528</v>
+        <v>3.37559563914273</v>
       </c>
     </row>
     <row r="399">
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="D399">
-        <v>10.8695652173913</v>
+        <v>10.97484690431897</v>
       </c>
     </row>
     <row r="400">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="D400">
-        <v>17.93478260869565</v>
+        <v>18.0278804413023</v>
       </c>
     </row>
     <row r="401">
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="D401">
-        <v>4.693877551020408</v>
+        <v>4.581185277148464</v>
       </c>
     </row>
     <row r="402">
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="D402">
-        <v>10.86538461538461</v>
+        <v>10.81283672770261</v>
       </c>
     </row>
     <row r="403">
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="D403">
-        <v>17.86036036036036</v>
+        <v>17.9935982753604</v>
       </c>
     </row>
     <row r="404">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="D404">
-        <v>4.952380952380953</v>
+        <v>4.934186690970451</v>
       </c>
     </row>
     <row r="405">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="D405">
-        <v>11.30841121495327</v>
+        <v>11.22056984272746</v>
       </c>
     </row>
     <row r="406">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="D406">
-        <v>19.91712220067008</v>
+        <v>19.85849852272626</v>
       </c>
     </row>
     <row r="407">
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="D407">
-        <v>4.215686274509804</v>
+        <v>4.029557112487895</v>
       </c>
     </row>
     <row r="408">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="D408">
-        <v>8.627450980392158</v>
+        <v>8.639624781724379</v>
       </c>
     </row>
     <row r="409">
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="D409">
-        <v>17.25274725274725</v>
+        <v>17.53347622893255</v>
       </c>
     </row>
     <row r="410">
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="D410">
-        <v>3.8</v>
+        <v>3.626849610830135</v>
       </c>
     </row>
     <row r="411">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="D411">
-        <v>10.48076923076923</v>
+        <v>10.50284793374692</v>
       </c>
     </row>
     <row r="412">
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="D412">
-        <v>20.27747252747253</v>
+        <v>20.59632101378336</v>
       </c>
     </row>
     <row r="413">
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="D413">
-        <v>4.285714285714286</v>
+        <v>4.294500614144154</v>
       </c>
     </row>
     <row r="414">
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="D414">
-        <v>11.47368421052632</v>
+        <v>11.52484868635352</v>
       </c>
     </row>
     <row r="415">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D415">
-        <v>20.5578947368421</v>
+        <v>20.53230790122646</v>
       </c>
     </row>
     <row r="416">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="D416">
-        <v>6.90721649484536</v>
+        <v>6.402419533311106</v>
       </c>
     </row>
     <row r="417">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="D417">
-        <v>14.91071428571428</v>
+        <v>15.10356602455456</v>
       </c>
     </row>
     <row r="418">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="D418">
-        <v>24.22222222222222</v>
+        <v>23.54727035881082</v>
       </c>
     </row>
     <row r="419">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="D419">
-        <v>4.016393442622951</v>
+        <v>3.807412917690085</v>
       </c>
     </row>
     <row r="420">
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="D420">
-        <v>11.27659574468085</v>
+        <v>11.16547803886123</v>
       </c>
     </row>
     <row r="421">
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="D421">
-        <v>20.47980894485454</v>
+        <v>20.06697707390957</v>
       </c>
     </row>
     <row r="422">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="D422">
-        <v>4.354838709677419</v>
+        <v>4.587460076341372</v>
       </c>
     </row>
     <row r="423">
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="D423">
-        <v>10.77669902912621</v>
+        <v>11.08242109863186</v>
       </c>
     </row>
     <row r="424">
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="D424">
-        <v>19.94156778137361</v>
+        <v>19.94577435339493</v>
       </c>
     </row>
     <row r="425">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="D425">
-        <v>3.867924528301887</v>
+        <v>3.831594574036286</v>
       </c>
     </row>
     <row r="426">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="D426">
-        <v>10.98039215686275</v>
+        <v>11.07376278420784</v>
       </c>
     </row>
     <row r="427">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="D427">
-        <v>17.15686274509804</v>
+        <v>16.91477925129175</v>
       </c>
     </row>
     <row r="428">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="D428">
-        <v>4.7</v>
+        <v>3.950260446787136</v>
       </c>
     </row>
     <row r="429">
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="D429">
-        <v>11.57303370786517</v>
+        <v>11.33701904348944</v>
       </c>
     </row>
     <row r="430">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="D430">
-        <v>22.31841894060995</v>
+        <v>22.44307622652039</v>
       </c>
     </row>
     <row r="431">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="D431">
-        <v>3.6</v>
+        <v>3.043680077718839</v>
       </c>
     </row>
     <row r="432">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="D432">
-        <v>10.10416666666667</v>
+        <v>10.28908648916008</v>
       </c>
     </row>
     <row r="433">
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="D433">
-        <v>23.10344827586207</v>
+        <v>22.82209788964152</v>
       </c>
     </row>
     <row r="434">
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="D434">
-        <v>5.169491525423728</v>
+        <v>5.023588352581966</v>
       </c>
     </row>
     <row r="435">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="D435">
-        <v>10.8695652173913</v>
+        <v>10.99161160927578</v>
       </c>
     </row>
     <row r="436">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="D436">
-        <v>22.24489795918367</v>
+        <v>22.22886093002493</v>
       </c>
     </row>
     <row r="437">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="D437">
-        <v>4.347826086956522</v>
+        <v>4.161074627852384</v>
       </c>
     </row>
     <row r="438">
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="D438">
-        <v>10.53097345132743</v>
+        <v>10.45896734458771</v>
       </c>
     </row>
     <row r="439">
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="D439">
-        <v>17.87610619469027</v>
+        <v>17.74170114596155</v>
       </c>
     </row>
     <row r="440">
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="D440">
-        <v>3.706896551724138</v>
+        <v>3.492168139204651</v>
       </c>
     </row>
     <row r="441">
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="D441">
-        <v>9.827586206896552</v>
+        <v>9.712740625035334</v>
       </c>
     </row>
     <row r="442">
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="D442">
-        <v>19.33333333333333</v>
+        <v>19.16846163399564</v>
       </c>
     </row>
     <row r="443">
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="D443">
-        <v>3.888888888888889</v>
+        <v>3.700555753989561</v>
       </c>
     </row>
     <row r="444">
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="D444">
-        <v>9.25925925925926</v>
+        <v>9.123522035509444</v>
       </c>
     </row>
     <row r="445">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="D445">
-        <v>18.13440142412105</v>
+        <v>18.015661777063</v>
       </c>
     </row>
     <row r="446">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="D446">
-        <v>4.6875</v>
+        <v>5.160821671864942</v>
       </c>
     </row>
     <row r="447">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="D447">
-        <v>11.25</v>
+        <v>10.95852161714424</v>
       </c>
     </row>
     <row r="448">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="D448">
-        <v>22.81818181818182</v>
+        <v>22.60274102149944</v>
       </c>
     </row>
     <row r="449">
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="D449">
-        <v>3.909090909090909</v>
+        <v>3.843117770882819</v>
       </c>
     </row>
     <row r="450">
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="D450">
-        <v>10.38961038961039</v>
+        <v>10.95357752799289</v>
       </c>
     </row>
     <row r="451">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="D451">
-        <v>25.13513513513513</v>
+        <v>24.7202568930232</v>
       </c>
     </row>
     <row r="452">
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="D452">
-        <v>6.990291262135922</v>
+        <v>6.722795450765901</v>
       </c>
     </row>
     <row r="453">
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="D453">
-        <v>15.19607843137255</v>
+        <v>15.20717333984185</v>
       </c>
     </row>
     <row r="454">
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="D454">
-        <v>26.22448979591837</v>
+        <v>25.9091822005293</v>
       </c>
     </row>
     <row r="455">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="D455">
-        <v>6.272727272727273</v>
+        <v>6.477665053242314</v>
       </c>
     </row>
     <row r="456">
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="D456">
-        <v>14.1025641025641</v>
+        <v>14.33858321675414</v>
       </c>
     </row>
     <row r="457">
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="D457">
-        <v>25.59139784946236</v>
+        <v>24.9722818531918</v>
       </c>
     </row>
     <row r="458">
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="D458">
-        <v>8.846153846153845</v>
+        <v>8.467230111083675</v>
       </c>
     </row>
     <row r="459">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="D459">
-        <v>17.93103448275862</v>
+        <v>17.70081523186025</v>
       </c>
     </row>
     <row r="460">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="D460">
-        <v>30.33333333333333</v>
+        <v>30.27804662788404</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
+++ b/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D460"/>
+  <dimension ref="A1:D649"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -3140,11 +3140,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>43466</v>
+        <v>45017</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3152,17 +3152,17 @@
         </is>
       </c>
       <c r="D155">
-        <v>4.681240774353519</v>
+        <v>4.701789321963692</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>43466</v>
+        <v>45017</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3170,17 +3170,17 @@
         </is>
       </c>
       <c r="D156">
-        <v>10.49899476091725</v>
+        <v>11.50619313963423</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>43466</v>
+        <v>45017</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3188,17 +3188,17 @@
         </is>
       </c>
       <c r="D157">
-        <v>17.64481398657003</v>
+        <v>23.8362160732075</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>43497</v>
+        <v>45047</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3206,17 +3206,17 @@
         </is>
       </c>
       <c r="D158">
-        <v>4.998216388852796</v>
+        <v>4.669626203897549</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>43497</v>
+        <v>45047</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3224,17 +3224,17 @@
         </is>
       </c>
       <c r="D159">
-        <v>8.992975962398614</v>
+        <v>11.83819342886537</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>43497</v>
+        <v>45047</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3242,17 +3242,17 @@
         </is>
       </c>
       <c r="D160">
-        <v>16.91299089986073</v>
+        <v>23.66382055652772</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>43525</v>
+        <v>45078</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3260,17 +3260,17 @@
         </is>
       </c>
       <c r="D161">
-        <v>4.710195275975137</v>
+        <v>4.19723193215585</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>43525</v>
+        <v>45078</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3278,17 +3278,17 @@
         </is>
       </c>
       <c r="D162">
-        <v>8.235936051110492</v>
+        <v>11.08834799079342</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>43525</v>
+        <v>45078</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
         </is>
       </c>
       <c r="D163">
-        <v>13.2411302449259</v>
+        <v>19.94322798482339</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>43556</v>
+        <v>45108</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3314,17 +3314,17 @@
         </is>
       </c>
       <c r="D164">
-        <v>5.235526350957272</v>
+        <v>5.616603539943764</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>43556</v>
+        <v>45108</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3332,17 +3332,17 @@
         </is>
       </c>
       <c r="D165">
-        <v>8.949504834993757</v>
+        <v>12.7079051197472</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>43556</v>
+        <v>45108</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3350,17 +3350,17 @@
         </is>
       </c>
       <c r="D166">
-        <v>16.10784446595772</v>
+        <v>21.22520650368471</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>43586</v>
+        <v>45139</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3368,17 +3368,17 @@
         </is>
       </c>
       <c r="D167">
-        <v>3.196380130816514</v>
+        <v>3.998856649117427</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>43586</v>
+        <v>45139</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3386,17 +3386,17 @@
         </is>
       </c>
       <c r="D168">
-        <v>7.947668778371127</v>
+        <v>11.18637044530531</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>43586</v>
+        <v>45139</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="D169">
-        <v>15.46346144337112</v>
+        <v>20.39842915808009</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>43617</v>
+        <v>45170</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3422,17 +3422,17 @@
         </is>
       </c>
       <c r="D170">
-        <v>4.022532286561306</v>
+        <v>4.255116225068593</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>43617</v>
+        <v>45170</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3440,17 +3440,17 @@
         </is>
       </c>
       <c r="D171">
-        <v>7.869762218194597</v>
+        <v>8.712244749991834</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>43617</v>
+        <v>45170</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3458,17 +3458,17 @@
         </is>
       </c>
       <c r="D172">
-        <v>14.72445759196292</v>
+        <v>17.65777206876521</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>43647</v>
+        <v>45200</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3476,17 +3476,17 @@
         </is>
       </c>
       <c r="D173">
-        <v>3.49482901715474</v>
+        <v>4.558212615143054</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>43647</v>
+        <v>45200</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3494,17 +3494,17 @@
         </is>
       </c>
       <c r="D174">
-        <v>7.282801826068171</v>
+        <v>10.69391685325569</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>43647</v>
+        <v>45200</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3512,17 +3512,17 @@
         </is>
       </c>
       <c r="D175">
-        <v>14.23668866607781</v>
+        <v>22.95350833658591</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>43678</v>
+        <v>45231</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3530,17 +3530,17 @@
         </is>
       </c>
       <c r="D176">
-        <v>3.325225000049993</v>
+        <v>3.836425484611329</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>43678</v>
+        <v>45231</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3548,17 +3548,17 @@
         </is>
       </c>
       <c r="D177">
-        <v>6.486997236306701</v>
+        <v>8.019353536894723</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>43678</v>
+        <v>45231</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="D178">
-        <v>15.40366242584833</v>
+        <v>16.12934616903992</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>43709</v>
+        <v>45261</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3584,17 +3584,17 @@
         </is>
       </c>
       <c r="D179">
-        <v>2.791974590910961</v>
+        <v>5.639378434784477</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>43709</v>
+        <v>45261</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3602,17 +3602,17 @@
         </is>
       </c>
       <c r="D180">
-        <v>6.545013357952921</v>
+        <v>11.65099245490214</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>43709</v>
+        <v>45261</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3620,17 +3620,17 @@
         </is>
       </c>
       <c r="D181">
-        <v>13.61850834705933</v>
+        <v>19.93556577103681</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>43739</v>
+        <v>45292</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3638,17 +3638,17 @@
         </is>
       </c>
       <c r="D182">
-        <v>5.910744964276597</v>
+        <v>4.760833512081142</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>43739</v>
+        <v>45292</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3656,17 +3656,17 @@
         </is>
       </c>
       <c r="D183">
-        <v>10.42089156632262</v>
+        <v>9.466203472610394</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>43739</v>
+        <v>45292</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3674,17 +3674,17 @@
         </is>
       </c>
       <c r="D184">
-        <v>19.05618097858698</v>
+        <v>16.74969770380805</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>43770</v>
+        <v>45323</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -3692,17 +3692,17 @@
         </is>
       </c>
       <c r="D185">
-        <v>6.156304370977379</v>
+        <v>4.204035824257472</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>43770</v>
+        <v>45323</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -3710,17 +3710,17 @@
         </is>
       </c>
       <c r="D186">
-        <v>10.21727871051709</v>
+        <v>9.746929318372372</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>43770</v>
+        <v>45323</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
         </is>
       </c>
       <c r="D187">
-        <v>16.36543205786478</v>
+        <v>17.57283745656924</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>43800</v>
+        <v>45352</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -3746,17 +3746,17 @@
         </is>
       </c>
       <c r="D188">
-        <v>3.741934778295222</v>
+        <v>2.474583479216321</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>43800</v>
+        <v>45352</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -3764,17 +3764,17 @@
         </is>
       </c>
       <c r="D189">
-        <v>6.861050172925603</v>
+        <v>6.72642579865734</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>43800</v>
+        <v>45352</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3782,17 +3782,17 @@
         </is>
       </c>
       <c r="D190">
-        <v>13.50810431690086</v>
+        <v>15.03424765743139</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>43831</v>
+        <v>45383</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3800,17 +3800,17 @@
         </is>
       </c>
       <c r="D191">
-        <v>5.588578148195052</v>
+        <v>3.092646569663897</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>43831</v>
+        <v>45383</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="D192">
-        <v>9.497517174436883</v>
+        <v>8.328060310127999</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>43831</v>
+        <v>45383</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3836,17 +3836,17 @@
         </is>
       </c>
       <c r="D193">
-        <v>18.82349772330201</v>
+        <v>15.89508549473013</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>43862</v>
+        <v>45413</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3854,17 +3854,17 @@
         </is>
       </c>
       <c r="D194">
-        <v>4.794821373123635</v>
+        <v>2.39000343906351</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>43862</v>
+        <v>45413</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3872,17 +3872,17 @@
         </is>
       </c>
       <c r="D195">
-        <v>6.96552905058366</v>
+        <v>8.502252535867395</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>43862</v>
+        <v>45413</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3890,17 +3890,17 @@
         </is>
       </c>
       <c r="D196">
-        <v>14.17243172900661</v>
+        <v>17.07579748157055</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>43891</v>
+        <v>45444</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3908,17 +3908,17 @@
         </is>
       </c>
       <c r="D197">
-        <v>10.75191004176526</v>
+        <v>2.304425043663738</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>43891</v>
+        <v>45444</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3926,17 +3926,17 @@
         </is>
       </c>
       <c r="D198">
-        <v>16.13736228032284</v>
+        <v>6.71147555389545</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>43891</v>
+        <v>45444</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3944,17 +3944,17 @@
         </is>
       </c>
       <c r="D199">
-        <v>30.29888299102025</v>
+        <v>14.42540475845484</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>43922</v>
+        <v>45474</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3962,17 +3962,17 @@
         </is>
       </c>
       <c r="D200">
-        <v>26.99287021510981</v>
+        <v>3.016237756293415</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>43922</v>
+        <v>45474</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3980,17 +3980,17 @@
         </is>
       </c>
       <c r="D201">
-        <v>36.63228126920093</v>
+        <v>9.397251293487672</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>43922</v>
+        <v>45474</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3998,17 +3998,17 @@
         </is>
       </c>
       <c r="D202">
-        <v>49.64962897103564</v>
+        <v>16.65473442512521</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>43952</v>
+        <v>45505</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -4016,17 +4016,17 @@
         </is>
       </c>
       <c r="D203">
-        <v>28.87353673562908</v>
+        <v>3.528440441623838</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>43952</v>
+        <v>45505</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -4034,17 +4034,17 @@
         </is>
       </c>
       <c r="D204">
-        <v>38.19373089771111</v>
+        <v>7.600513611199126</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>43952</v>
+        <v>45505</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4052,17 +4052,17 @@
         </is>
       </c>
       <c r="D205">
-        <v>51.35785511064351</v>
+        <v>16.35030528247785</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>43983</v>
+        <v>45536</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -4070,17 +4070,17 @@
         </is>
       </c>
       <c r="D206">
-        <v>23.22657136684287</v>
+        <v>2.580149716855877</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>43983</v>
+        <v>45536</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -4088,17 +4088,17 @@
         </is>
       </c>
       <c r="D207">
-        <v>31.93209007869573</v>
+        <v>6.245858335982907</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>43983</v>
+        <v>45536</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4106,17 +4106,17 @@
         </is>
       </c>
       <c r="D208">
-        <v>47.07416008101185</v>
+        <v>12.12711593474468</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>44013</v>
+        <v>45566</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -4124,17 +4124,17 @@
         </is>
       </c>
       <c r="D209">
-        <v>22.46118574564798</v>
+        <v>2.360248888779608</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>44013</v>
+        <v>45566</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -4142,17 +4142,17 @@
         </is>
       </c>
       <c r="D210">
-        <v>32.1511019488425</v>
+        <v>6.03471756185566</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>44013</v>
+        <v>45566</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4160,17 +4160,17 @@
         </is>
       </c>
       <c r="D211">
-        <v>44.67031621245329</v>
+        <v>12.91042433930012</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>44044</v>
+        <v>45597</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -4178,17 +4178,17 @@
         </is>
       </c>
       <c r="D212">
-        <v>12.51936666560602</v>
+        <v>1.451989343655744</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>44044</v>
+        <v>45597</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -4196,17 +4196,17 @@
         </is>
       </c>
       <c r="D213">
-        <v>19.20141585249397</v>
+        <v>6.008954828040355</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>44044</v>
+        <v>45597</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4214,17 +4214,17 @@
         </is>
       </c>
       <c r="D214">
-        <v>31.12543076533419</v>
+        <v>12.67485794514874</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>44075</v>
+        <v>45627</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="D215">
-        <v>7.398399087871278</v>
+        <v>3.512008363774798</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>44075</v>
+        <v>45627</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -4250,17 +4250,17 @@
         </is>
       </c>
       <c r="D216">
-        <v>14.73390433792328</v>
+        <v>8.481213239668342</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>44075</v>
+        <v>45627</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="D217">
-        <v>28.273174701977</v>
+        <v>16.87160345608657</v>
       </c>
     </row>
     <row r="218">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B218" s="2">
-        <v>44105</v>
+        <v>43466</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>7.669408975312855</v>
+        <v>4.681240774353519</v>
       </c>
     </row>
     <row r="219">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="B219" s="2">
-        <v>44105</v>
+        <v>43466</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="D219">
-        <v>14.76466615963838</v>
+        <v>10.49899476091725</v>
       </c>
     </row>
     <row r="220">
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="B220" s="2">
-        <v>44105</v>
+        <v>43466</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>26.28341171869635</v>
+        <v>17.64481398657003</v>
       </c>
     </row>
     <row r="221">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="B221" s="2">
-        <v>44136</v>
+        <v>43497</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="D221">
-        <v>6.524543409419688</v>
+        <v>4.998216388852796</v>
       </c>
     </row>
     <row r="222">
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="B222" s="2">
-        <v>44136</v>
+        <v>43497</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>11.47174402640319</v>
+        <v>8.992975962398614</v>
       </c>
     </row>
     <row r="223">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="B223" s="2">
-        <v>44136</v>
+        <v>43497</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>25.05885768223203</v>
+        <v>16.91299089986073</v>
       </c>
     </row>
     <row r="224">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="B224" s="2">
-        <v>44166</v>
+        <v>43525</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>6.298370128966183</v>
+        <v>4.710195275975137</v>
       </c>
     </row>
     <row r="225">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="B225" s="2">
-        <v>44166</v>
+        <v>43525</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>11.95383968314153</v>
+        <v>8.235936051110492</v>
       </c>
     </row>
     <row r="226">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="B226" s="2">
-        <v>44166</v>
+        <v>43525</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>23.59421550099251</v>
+        <v>13.2411302449259</v>
       </c>
     </row>
     <row r="227">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="B227" s="2">
-        <v>44197</v>
+        <v>43556</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="D227">
-        <v>7.509042630898817</v>
+        <v>5.235526350957272</v>
       </c>
     </row>
     <row r="228">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="B228" s="2">
-        <v>44197</v>
+        <v>43556</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>12.75839874800015</v>
+        <v>8.949504834993757</v>
       </c>
     </row>
     <row r="229">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="B229" s="2">
-        <v>44197</v>
+        <v>43556</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="D229">
-        <v>25.98648760649906</v>
+        <v>16.10784446595772</v>
       </c>
     </row>
     <row r="230">
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="B230" s="2">
-        <v>44228</v>
+        <v>43586</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D230">
-        <v>7.437866721185186</v>
+        <v>3.196380130816514</v>
       </c>
     </row>
     <row r="231">
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="B231" s="2">
-        <v>44228</v>
+        <v>43586</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="D231">
-        <v>12.29688385478446</v>
+        <v>7.947668778371127</v>
       </c>
     </row>
     <row r="232">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B232" s="2">
-        <v>44228</v>
+        <v>43586</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="D232">
-        <v>24.68463435658308</v>
+        <v>15.46346144337112</v>
       </c>
     </row>
     <row r="233">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="B233" s="2">
-        <v>44256</v>
+        <v>43617</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>5.091795183289094</v>
+        <v>4.022532286561306</v>
       </c>
     </row>
     <row r="234">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="B234" s="2">
-        <v>44256</v>
+        <v>43617</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>10.27813742634264</v>
+        <v>7.869762218194597</v>
       </c>
     </row>
     <row r="235">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="B235" s="2">
-        <v>44256</v>
+        <v>43617</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>20.80877283752077</v>
+        <v>14.72445759196292</v>
       </c>
     </row>
     <row r="236">
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="B236" s="2">
-        <v>44287</v>
+        <v>43647</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>8.761263547790453</v>
+        <v>3.49482901715474</v>
       </c>
     </row>
     <row r="237">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B237" s="2">
-        <v>44287</v>
+        <v>43647</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>15.93943892205238</v>
+        <v>7.282801826068171</v>
       </c>
     </row>
     <row r="238">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="B238" s="2">
-        <v>44287</v>
+        <v>43647</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="D238">
-        <v>29.71661667942666</v>
+        <v>14.23668866607781</v>
       </c>
     </row>
     <row r="239">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="B239" s="2">
-        <v>44317</v>
+        <v>43678</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="D239">
-        <v>9.852095188357314</v>
+        <v>3.325225000049993</v>
       </c>
     </row>
     <row r="240">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="B240" s="2">
-        <v>44317</v>
+        <v>43678</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>19.29812718502892</v>
+        <v>6.486997236306701</v>
       </c>
     </row>
     <row r="241">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="B241" s="2">
-        <v>44317</v>
+        <v>43678</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D241">
-        <v>34.12378122989298</v>
+        <v>15.40366242584833</v>
       </c>
     </row>
     <row r="242">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="B242" s="2">
-        <v>44348</v>
+        <v>43709</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D242">
-        <v>10.38681001141584</v>
+        <v>2.791974590910961</v>
       </c>
     </row>
     <row r="243">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="B243" s="2">
-        <v>44348</v>
+        <v>43709</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="D243">
-        <v>17.33301201115656</v>
+        <v>6.545013357952921</v>
       </c>
     </row>
     <row r="244">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="B244" s="2">
-        <v>44348</v>
+        <v>43709</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="D244">
-        <v>28.82460723966872</v>
+        <v>13.61850834705933</v>
       </c>
     </row>
     <row r="245">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="B245" s="2">
-        <v>44378</v>
+        <v>43739</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D245">
-        <v>6.2250701788204</v>
+        <v>5.910744964276597</v>
       </c>
     </row>
     <row r="246">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="B246" s="2">
-        <v>44378</v>
+        <v>43739</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="D246">
-        <v>12.7488034454403</v>
+        <v>10.42089156632262</v>
       </c>
     </row>
     <row r="247">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="B247" s="2">
-        <v>44378</v>
+        <v>43739</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>25.17275951157797</v>
+        <v>19.05618097858698</v>
       </c>
     </row>
     <row r="248">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="B248" s="2">
-        <v>44409</v>
+        <v>43770</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="D248">
-        <v>4.870339811481849</v>
+        <v>6.156304370977379</v>
       </c>
     </row>
     <row r="249">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="B249" s="2">
-        <v>44409</v>
+        <v>43770</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>11.86231183874567</v>
+        <v>10.21727871051709</v>
       </c>
     </row>
     <row r="250">
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="B250" s="2">
-        <v>44409</v>
+        <v>43770</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="D250">
-        <v>23.59252762714859</v>
+        <v>16.36543205786478</v>
       </c>
     </row>
     <row r="251">
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="B251" s="2">
-        <v>44440</v>
+        <v>43800</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="D251">
-        <v>4.692932006581518</v>
+        <v>3.741934778295222</v>
       </c>
     </row>
     <row r="252">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="B252" s="2">
-        <v>44440</v>
+        <v>43800</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="D252">
-        <v>10.87534677620336</v>
+        <v>6.861050172925603</v>
       </c>
     </row>
     <row r="253">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="B253" s="2">
-        <v>44440</v>
+        <v>43800</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="D253">
-        <v>22.96845744140189</v>
+        <v>13.50810431690086</v>
       </c>
     </row>
     <row r="254">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="B254" s="2">
-        <v>44470</v>
+        <v>43831</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="D254">
-        <v>5.750330029007619</v>
+        <v>5.588578148195052</v>
       </c>
     </row>
     <row r="255">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="B255" s="2">
-        <v>44470</v>
+        <v>43831</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>13.39216337198151</v>
+        <v>9.497517174436883</v>
       </c>
     </row>
     <row r="256">
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="B256" s="2">
-        <v>44470</v>
+        <v>43831</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>25.57975540008733</v>
+        <v>18.82349772330201</v>
       </c>
     </row>
     <row r="257">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="B257" s="2">
-        <v>44501</v>
+        <v>43862</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D257">
-        <v>4.554715414664873</v>
+        <v>4.794821373123635</v>
       </c>
     </row>
     <row r="258">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="B258" s="2">
-        <v>44501</v>
+        <v>43862</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D258">
-        <v>12.01721950947282</v>
+        <v>6.96552905058366</v>
       </c>
     </row>
     <row r="259">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="B259" s="2">
-        <v>44501</v>
+        <v>43862</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="D259">
-        <v>25.40609176315192</v>
+        <v>14.17243172900661</v>
       </c>
     </row>
     <row r="260">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="B260" s="2">
-        <v>44531</v>
+        <v>43891</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="D260">
-        <v>4.052687448111717</v>
+        <v>10.75191004176526</v>
       </c>
     </row>
     <row r="261">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="B261" s="2">
-        <v>44531</v>
+        <v>43891</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D261">
-        <v>11.55527915565783</v>
+        <v>16.13736228032284</v>
       </c>
     </row>
     <row r="262">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="B262" s="2">
-        <v>44531</v>
+        <v>43891</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D262">
-        <v>22.53085488146424</v>
+        <v>30.29888299102025</v>
       </c>
     </row>
     <row r="263">
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="B263" s="2">
-        <v>44562</v>
+        <v>43922</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="D263">
-        <v>6.631495269336487</v>
+        <v>26.99287021510981</v>
       </c>
     </row>
     <row r="264">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="B264" s="2">
-        <v>44562</v>
+        <v>43922</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="D264">
-        <v>15.80951272965379</v>
+        <v>36.63228126920093</v>
       </c>
     </row>
     <row r="265">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="B265" s="2">
-        <v>44562</v>
+        <v>43922</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D265">
-        <v>26.67158202877681</v>
+        <v>49.64962897103564</v>
       </c>
     </row>
     <row r="266">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="B266" s="2">
-        <v>44593</v>
+        <v>43952</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D266">
-        <v>5.349214410339786</v>
+        <v>28.87353673562908</v>
       </c>
     </row>
     <row r="267">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="B267" s="2">
-        <v>44593</v>
+        <v>43952</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="D267">
-        <v>14.62757879511282</v>
+        <v>38.19373089771111</v>
       </c>
     </row>
     <row r="268">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="B268" s="2">
-        <v>44593</v>
+        <v>43952</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="D268">
-        <v>25.89245680910768</v>
+        <v>51.35785511064351</v>
       </c>
     </row>
     <row r="269">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="B269" s="2">
-        <v>44621</v>
+        <v>43983</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="D269">
-        <v>4.206235538194951</v>
+        <v>23.22657136684287</v>
       </c>
     </row>
     <row r="270">
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="B270" s="2">
-        <v>44621</v>
+        <v>43983</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="D270">
-        <v>12.0618334226017</v>
+        <v>31.93209007869573</v>
       </c>
     </row>
     <row r="271">
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="B271" s="2">
-        <v>44621</v>
+        <v>43983</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D271">
-        <v>24.74337155321622</v>
+        <v>47.07416008101185</v>
       </c>
     </row>
     <row r="272">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B272" s="2">
-        <v>44652</v>
+        <v>44013</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="D272">
-        <v>3.709355861878632</v>
+        <v>22.46118574564798</v>
       </c>
     </row>
     <row r="273">
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="B273" s="2">
-        <v>44652</v>
+        <v>44013</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="D273">
-        <v>10</v>
+        <v>32.1511019488425</v>
       </c>
     </row>
     <row r="274">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="B274" s="2">
-        <v>44652</v>
+        <v>44013</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="D274">
-        <v>21.8791295432245</v>
+        <v>44.67031621245329</v>
       </c>
     </row>
     <row r="275">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="B275" s="2">
-        <v>44682</v>
+        <v>44044</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D275">
-        <v>6.345464025894161</v>
+        <v>12.51936666560602</v>
       </c>
     </row>
     <row r="276">
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="B276" s="2">
-        <v>44682</v>
+        <v>44044</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D276">
-        <v>12.39391008263184</v>
+        <v>19.20141585249397</v>
       </c>
     </row>
     <row r="277">
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="B277" s="2">
-        <v>44682</v>
+        <v>44044</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="D277">
-        <v>23.49786130959714</v>
+        <v>31.12543076533419</v>
       </c>
     </row>
     <row r="278">
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="B278" s="2">
-        <v>44713</v>
+        <v>44075</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="D278">
-        <v>4.878418981092032</v>
+        <v>7.398399087871278</v>
       </c>
     </row>
     <row r="279">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="B279" s="2">
-        <v>44713</v>
+        <v>44075</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="D279">
-        <v>13.42662363267418</v>
+        <v>14.73390433792328</v>
       </c>
     </row>
     <row r="280">
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="B280" s="2">
-        <v>44713</v>
+        <v>44075</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="D280">
-        <v>26.63842203846296</v>
+        <v>28.273174701977</v>
       </c>
     </row>
     <row r="281">
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="B281" s="2">
-        <v>44743</v>
+        <v>44105</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="D281">
-        <v>5.384383297946298</v>
+        <v>7.669408975312855</v>
       </c>
     </row>
     <row r="282">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="B282" s="2">
-        <v>44743</v>
+        <v>44105</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>14.70783525380426</v>
+        <v>14.76466615963838</v>
       </c>
     </row>
     <row r="283">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="B283" s="2">
-        <v>44743</v>
+        <v>44105</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="D283">
-        <v>26.03741143059548</v>
+        <v>26.28341171869635</v>
       </c>
     </row>
     <row r="284">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="B284" s="2">
-        <v>44774</v>
+        <v>44136</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D284">
-        <v>4.683728334505173</v>
+        <v>6.524543409419688</v>
       </c>
     </row>
     <row r="285">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="B285" s="2">
-        <v>44774</v>
+        <v>44136</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>13.47970289847173</v>
+        <v>11.47174402640319</v>
       </c>
     </row>
     <row r="286">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="B286" s="2">
-        <v>44774</v>
+        <v>44136</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="D286">
-        <v>25.75165670000204</v>
+        <v>25.05885768223203</v>
       </c>
     </row>
     <row r="287">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="B287" s="2">
-        <v>44805</v>
+        <v>44166</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="D287">
-        <v>5.414723938960424</v>
+        <v>6.298370128966183</v>
       </c>
     </row>
     <row r="288">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="B288" s="2">
-        <v>44805</v>
+        <v>44166</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="D288">
-        <v>13.99874069065162</v>
+        <v>11.95383968314153</v>
       </c>
     </row>
     <row r="289">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="B289" s="2">
-        <v>44805</v>
+        <v>44166</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D289">
-        <v>26.63663052448497</v>
+        <v>23.59421550099251</v>
       </c>
     </row>
     <row r="290">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="B290" s="2">
-        <v>44835</v>
+        <v>44197</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="D290">
-        <v>4.516270678962129</v>
+        <v>7.509042630898817</v>
       </c>
     </row>
     <row r="291">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="B291" s="2">
-        <v>44835</v>
+        <v>44197</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="D291">
-        <v>11.31250897362911</v>
+        <v>12.75839874800015</v>
       </c>
     </row>
     <row r="292">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="B292" s="2">
-        <v>44835</v>
+        <v>44197</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="D292">
-        <v>21.89119592618533</v>
+        <v>25.98648760649906</v>
       </c>
     </row>
     <row r="293">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="B293" s="2">
-        <v>44866</v>
+        <v>44228</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="D293">
-        <v>5.420596950183324</v>
+        <v>7.437866721185186</v>
       </c>
     </row>
     <row r="294">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="B294" s="2">
-        <v>44866</v>
+        <v>44228</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="D294">
-        <v>13.78237899001062</v>
+        <v>12.29688385478446</v>
       </c>
     </row>
     <row r="295">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="B295" s="2">
-        <v>44866</v>
+        <v>44228</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D295">
-        <v>28.12282628257245</v>
+        <v>24.68463435658308</v>
       </c>
     </row>
     <row r="296">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="B296" s="2">
-        <v>44896</v>
+        <v>44256</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="D296">
-        <v>6.101883046427322</v>
+        <v>5.091795183289094</v>
       </c>
     </row>
     <row r="297">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="B297" s="2">
-        <v>44896</v>
+        <v>44256</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="D297">
-        <v>14.46429996756167</v>
+        <v>10.27813742634264</v>
       </c>
     </row>
     <row r="298">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B298" s="2">
-        <v>44896</v>
+        <v>44256</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="D298">
-        <v>25.91758966708806</v>
+        <v>20.80877283752077</v>
       </c>
     </row>
     <row r="299">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="B299" s="2">
-        <v>44927</v>
+        <v>44287</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="D299">
-        <v>7.83871394270524</v>
+        <v>8.761263547790453</v>
       </c>
     </row>
     <row r="300">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B300" s="2">
-        <v>44927</v>
+        <v>44287</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="D300">
-        <v>18.25116173820857</v>
+        <v>15.93943892205238</v>
       </c>
     </row>
     <row r="301">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="B301" s="2">
-        <v>44927</v>
+        <v>44287</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="D301">
-        <v>29.21485334505552</v>
+        <v>29.71661667942666</v>
       </c>
     </row>
     <row r="302">
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="B302" s="2">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="D302">
-        <v>6.014338832325178</v>
+        <v>9.852095188357314</v>
       </c>
     </row>
     <row r="303">
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="B303" s="2">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="D303">
-        <v>16.82365063925133</v>
+        <v>19.29812718502892</v>
       </c>
     </row>
     <row r="304">
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="B304" s="2">
-        <v>44958</v>
+        <v>44317</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="D304">
-        <v>31.02424420233584</v>
+        <v>34.12378122989298</v>
       </c>
     </row>
     <row r="305">
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="B305" s="2">
-        <v>44986</v>
+        <v>44348</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D305">
-        <v>8.219005805999657</v>
+        <v>10.38681001141584</v>
       </c>
     </row>
     <row r="306">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="B306" s="2">
-        <v>44986</v>
+        <v>44348</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="D306">
-        <v>19.66228489123335</v>
+        <v>17.33301201115656</v>
       </c>
     </row>
     <row r="307">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="B307" s="2">
-        <v>44986</v>
+        <v>44348</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -5888,17 +5888,17 @@
         </is>
       </c>
       <c r="D307">
-        <v>33.36730743687373</v>
+        <v>28.82460723966872</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B308" s="2">
-        <v>43466</v>
+        <v>44378</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -5906,17 +5906,17 @@
         </is>
       </c>
       <c r="D308">
-        <v>3.6349493549969</v>
+        <v>6.2250701788204</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B309" s="2">
-        <v>43466</v>
+        <v>44378</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -5924,17 +5924,17 @@
         </is>
       </c>
       <c r="D309">
-        <v>10.11050115125111</v>
+        <v>12.7488034454403</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B310" s="2">
-        <v>43466</v>
+        <v>44378</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -5942,17 +5942,17 @@
         </is>
       </c>
       <c r="D310">
-        <v>16.42017499049537</v>
+        <v>25.17275951157797</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B311" s="2">
-        <v>43497</v>
+        <v>44409</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -5960,17 +5960,17 @@
         </is>
       </c>
       <c r="D311">
-        <v>3.977230540665857</v>
+        <v>4.870339811481849</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B312" s="2">
-        <v>43497</v>
+        <v>44409</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5978,17 +5978,17 @@
         </is>
       </c>
       <c r="D312">
-        <v>8.238228207578885</v>
+        <v>11.86231183874567</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B313" s="2">
-        <v>43497</v>
+        <v>44409</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5996,17 +5996,17 @@
         </is>
       </c>
       <c r="D313">
-        <v>15.42942871566926</v>
+        <v>23.59252762714859</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B314" s="2">
-        <v>43525</v>
+        <v>44440</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6014,17 +6014,17 @@
         </is>
       </c>
       <c r="D314">
-        <v>3.425208838612741</v>
+        <v>4.692932006581518</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B315" s="2">
-        <v>43525</v>
+        <v>44440</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -6032,17 +6032,17 @@
         </is>
       </c>
       <c r="D315">
-        <v>8.026509093648716</v>
+        <v>10.87534677620336</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B316" s="2">
-        <v>43525</v>
+        <v>44440</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -6050,17 +6050,17 @@
         </is>
       </c>
       <c r="D316">
-        <v>13.83632104810355</v>
+        <v>22.96845744140189</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B317" s="2">
-        <v>43556</v>
+        <v>44470</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -6068,17 +6068,17 @@
         </is>
       </c>
       <c r="D317">
-        <v>3.218378908891774</v>
+        <v>5.750330029007619</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B318" s="2">
-        <v>43556</v>
+        <v>44470</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -6086,17 +6086,17 @@
         </is>
       </c>
       <c r="D318">
-        <v>7.866500759283099</v>
+        <v>13.39216337198151</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B319" s="2">
-        <v>43556</v>
+        <v>44470</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -6104,17 +6104,17 @@
         </is>
       </c>
       <c r="D319">
-        <v>13.23195813812105</v>
+        <v>25.57975540008733</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B320" s="2">
-        <v>43586</v>
+        <v>44501</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -6122,17 +6122,17 @@
         </is>
       </c>
       <c r="D320">
-        <v>3.766302624944184</v>
+        <v>4.554715414664873</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B321" s="2">
-        <v>43586</v>
+        <v>44501</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -6140,17 +6140,17 @@
         </is>
       </c>
       <c r="D321">
-        <v>7.634820589984834</v>
+        <v>12.01721950947282</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B322" s="2">
-        <v>43586</v>
+        <v>44501</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -6158,17 +6158,17 @@
         </is>
       </c>
       <c r="D322">
-        <v>14.04745597323936</v>
+        <v>25.40609176315192</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B323" s="2">
-        <v>43617</v>
+        <v>44531</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -6176,17 +6176,17 @@
         </is>
       </c>
       <c r="D323">
-        <v>3.458306529438883</v>
+        <v>4.052687448111717</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B324" s="2">
-        <v>43617</v>
+        <v>44531</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -6194,17 +6194,17 @@
         </is>
       </c>
       <c r="D324">
-        <v>6.710999456412623</v>
+        <v>11.55527915565783</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B325" s="2">
-        <v>43617</v>
+        <v>44531</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -6212,17 +6212,17 @@
         </is>
       </c>
       <c r="D325">
-        <v>12.28850060630379</v>
+        <v>22.53085488146424</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B326" s="2">
-        <v>43647</v>
+        <v>44562</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -6230,17 +6230,17 @@
         </is>
       </c>
       <c r="D326">
-        <v>3.128694008579072</v>
+        <v>6.631495269336487</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B327" s="2">
-        <v>43647</v>
+        <v>44562</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -6248,17 +6248,17 @@
         </is>
       </c>
       <c r="D327">
-        <v>7.225202870356553</v>
+        <v>15.80951272965379</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B328" s="2">
-        <v>43647</v>
+        <v>44562</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -6266,17 +6266,17 @@
         </is>
       </c>
       <c r="D328">
-        <v>12.82281884062744</v>
+        <v>26.67158202877681</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B329" s="2">
-        <v>43678</v>
+        <v>44593</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -6284,17 +6284,17 @@
         </is>
       </c>
       <c r="D329">
-        <v>3.536389176905308</v>
+        <v>5.349214410339786</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B330" s="2">
-        <v>43678</v>
+        <v>44593</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -6302,17 +6302,17 @@
         </is>
       </c>
       <c r="D330">
-        <v>7.064997935219369</v>
+        <v>14.62757879511282</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B331" s="2">
-        <v>43678</v>
+        <v>44593</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -6320,17 +6320,17 @@
         </is>
       </c>
       <c r="D331">
-        <v>11.19374909605078</v>
+        <v>25.89245680910768</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B332" s="2">
-        <v>43709</v>
+        <v>44621</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -6338,17 +6338,17 @@
         </is>
       </c>
       <c r="D332">
-        <v>3.517101731044673</v>
+        <v>4.206235538194951</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B333" s="2">
-        <v>43709</v>
+        <v>44621</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -6356,17 +6356,17 @@
         </is>
       </c>
       <c r="D333">
-        <v>7.450481302466693</v>
+        <v>12.0618334226017</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B334" s="2">
-        <v>43709</v>
+        <v>44621</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -6374,17 +6374,17 @@
         </is>
       </c>
       <c r="D334">
-        <v>13.70987075558255</v>
+        <v>24.74337155321622</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B335" s="2">
-        <v>43739</v>
+        <v>44652</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -6392,17 +6392,17 @@
         </is>
       </c>
       <c r="D335">
-        <v>2.44455895400372</v>
+        <v>3.709355861878632</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B336" s="2">
-        <v>43739</v>
+        <v>44652</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -6410,17 +6410,17 @@
         </is>
       </c>
       <c r="D336">
-        <v>5.216849297711635</v>
+        <v>10</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B337" s="2">
-        <v>43739</v>
+        <v>44652</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -6428,17 +6428,17 @@
         </is>
       </c>
       <c r="D337">
-        <v>11.40182503458006</v>
+        <v>21.8791295432245</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B338" s="2">
-        <v>43770</v>
+        <v>44682</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -6446,17 +6446,17 @@
         </is>
       </c>
       <c r="D338">
-        <v>2.531755231569268</v>
+        <v>6.345464025894161</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B339" s="2">
-        <v>43770</v>
+        <v>44682</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -6464,17 +6464,17 @@
         </is>
       </c>
       <c r="D339">
-        <v>5.541244937880761</v>
+        <v>12.39391008263184</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B340" s="2">
-        <v>43770</v>
+        <v>44682</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -6482,17 +6482,17 @@
         </is>
       </c>
       <c r="D340">
-        <v>11.67915398099378</v>
+        <v>23.49786130959714</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B341" s="2">
-        <v>43800</v>
+        <v>44713</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -6500,17 +6500,17 @@
         </is>
       </c>
       <c r="D341">
-        <v>4.03390565677894</v>
+        <v>4.878418981092032</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B342" s="2">
-        <v>43800</v>
+        <v>44713</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -6518,17 +6518,17 @@
         </is>
       </c>
       <c r="D342">
-        <v>7.082203851823957</v>
+        <v>13.42662363267418</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B343" s="2">
-        <v>43800</v>
+        <v>44713</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -6536,17 +6536,17 @@
         </is>
       </c>
       <c r="D343">
-        <v>14.33674175848242</v>
+        <v>26.63842203846296</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B344" s="2">
-        <v>43831</v>
+        <v>44743</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -6554,17 +6554,17 @@
         </is>
       </c>
       <c r="D344">
-        <v>2.81015544718536</v>
+        <v>5.384383297946298</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B345" s="2">
-        <v>43831</v>
+        <v>44743</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -6572,17 +6572,17 @@
         </is>
       </c>
       <c r="D345">
-        <v>5.574891248144008</v>
+        <v>14.70783525380426</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B346" s="2">
-        <v>43831</v>
+        <v>44743</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -6590,17 +6590,17 @@
         </is>
       </c>
       <c r="D346">
-        <v>10.21530757732704</v>
+        <v>26.03741143059548</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B347" s="2">
-        <v>43862</v>
+        <v>44774</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -6608,17 +6608,17 @@
         </is>
       </c>
       <c r="D347">
-        <v>4.165757989575734</v>
+        <v>4.683728334505173</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B348" s="2">
-        <v>43862</v>
+        <v>44774</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -6626,17 +6626,17 @@
         </is>
       </c>
       <c r="D348">
-        <v>8.211029338959245</v>
+        <v>13.47970289847173</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B349" s="2">
-        <v>43862</v>
+        <v>44774</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -6644,17 +6644,17 @@
         </is>
       </c>
       <c r="D349">
-        <v>13.67698510560965</v>
+        <v>25.75165670000204</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B350" s="2">
-        <v>43891</v>
+        <v>44805</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -6662,17 +6662,17 @@
         </is>
       </c>
       <c r="D350">
-        <v>8.007656954473042</v>
+        <v>5.414723938960424</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B351" s="2">
-        <v>43891</v>
+        <v>44805</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -6680,17 +6680,17 @@
         </is>
       </c>
       <c r="D351">
-        <v>13.2793373091607</v>
+        <v>13.99874069065162</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B352" s="2">
-        <v>43891</v>
+        <v>44805</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -6698,17 +6698,17 @@
         </is>
       </c>
       <c r="D352">
-        <v>19.0099697292832</v>
+        <v>26.63663052448497</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B353" s="2">
-        <v>43922</v>
+        <v>44835</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
         </is>
       </c>
       <c r="D353">
-        <v>14.65089536566943</v>
+        <v>4.516270678962129</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B354" s="2">
-        <v>43922</v>
+        <v>44835</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -6734,17 +6734,17 @@
         </is>
       </c>
       <c r="D354">
-        <v>22.85772977244308</v>
+        <v>11.31250897362911</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B355" s="2">
-        <v>43922</v>
+        <v>44835</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -6752,17 +6752,17 @@
         </is>
       </c>
       <c r="D355">
-        <v>34.64756870116229</v>
+        <v>21.89119592618533</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B356" s="2">
-        <v>43952</v>
+        <v>44866</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -6770,17 +6770,17 @@
         </is>
       </c>
       <c r="D356">
-        <v>18.65634538780538</v>
+        <v>5.420596950183324</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B357" s="2">
-        <v>43952</v>
+        <v>44866</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -6788,17 +6788,17 @@
         </is>
       </c>
       <c r="D357">
-        <v>27.84260654062342</v>
+        <v>13.78237899001062</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B358" s="2">
-        <v>43952</v>
+        <v>44866</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -6806,17 +6806,17 @@
         </is>
       </c>
       <c r="D358">
-        <v>38.93451674663208</v>
+        <v>28.12282628257245</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B359" s="2">
-        <v>43983</v>
+        <v>44896</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -6824,17 +6824,17 @@
         </is>
       </c>
       <c r="D359">
-        <v>16.77730646300213</v>
+        <v>6.101883046427322</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B360" s="2">
-        <v>43983</v>
+        <v>44896</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -6842,17 +6842,17 @@
         </is>
       </c>
       <c r="D360">
-        <v>27.04594074295498</v>
+        <v>14.46429996756167</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B361" s="2">
-        <v>43983</v>
+        <v>44896</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -6860,17 +6860,17 @@
         </is>
       </c>
       <c r="D361">
-        <v>37.3933252883466</v>
+        <v>25.91758966708806</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B362" s="2">
-        <v>44013</v>
+        <v>44927</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -6878,17 +6878,17 @@
         </is>
       </c>
       <c r="D362">
-        <v>14.69866124001517</v>
+        <v>7.83871394270524</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B363" s="2">
-        <v>44013</v>
+        <v>44927</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -6896,17 +6896,17 @@
         </is>
       </c>
       <c r="D363">
-        <v>23.6845758843451</v>
+        <v>18.25116173820857</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B364" s="2">
-        <v>44013</v>
+        <v>44927</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -6914,17 +6914,17 @@
         </is>
       </c>
       <c r="D364">
-        <v>34.79729326724932</v>
+        <v>29.21485334505552</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B365" s="2">
-        <v>44044</v>
+        <v>44958</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -6932,17 +6932,17 @@
         </is>
       </c>
       <c r="D365">
-        <v>10.28042905307037</v>
+        <v>6.014338832325178</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B366" s="2">
-        <v>44044</v>
+        <v>44958</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -6950,17 +6950,17 @@
         </is>
       </c>
       <c r="D366">
-        <v>17.70557193198582</v>
+        <v>16.82365063925133</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B367" s="2">
-        <v>44044</v>
+        <v>44958</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -6968,17 +6968,17 @@
         </is>
       </c>
       <c r="D367">
-        <v>29.00573638579855</v>
+        <v>31.02424420233584</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B368" s="2">
-        <v>44075</v>
+        <v>44986</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -6986,17 +6986,17 @@
         </is>
       </c>
       <c r="D368">
-        <v>6.474743825349387</v>
+        <v>8.219005805999657</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B369" s="2">
-        <v>44075</v>
+        <v>44986</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -7004,17 +7004,17 @@
         </is>
       </c>
       <c r="D369">
-        <v>12.96943714885955</v>
+        <v>19.66228489123335</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B370" s="2">
-        <v>44075</v>
+        <v>44986</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -7022,17 +7022,17 @@
         </is>
       </c>
       <c r="D370">
-        <v>21.69657673954115</v>
+        <v>33.36730743687373</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B371" s="2">
-        <v>44105</v>
+        <v>45017</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -7040,17 +7040,17 @@
         </is>
       </c>
       <c r="D371">
-        <v>4.873547040611218</v>
+        <v>5.577586405890628</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B372" s="2">
-        <v>44105</v>
+        <v>45017</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="D372">
-        <v>12.16941138926549</v>
+        <v>17.24405480393601</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B373" s="2">
-        <v>44105</v>
+        <v>45017</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -7076,17 +7076,17 @@
         </is>
       </c>
       <c r="D373">
-        <v>19.29075592179443</v>
+        <v>30.45560871051813</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B374" s="2">
-        <v>44136</v>
+        <v>45047</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -7094,17 +7094,17 @@
         </is>
       </c>
       <c r="D374">
-        <v>5.441884722788836</v>
+        <v>4.943221910707535</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B375" s="2">
-        <v>44136</v>
+        <v>45047</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -7112,17 +7112,17 @@
         </is>
       </c>
       <c r="D375">
-        <v>9.104773457233595</v>
+        <v>15.95363274769398</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B376" s="2">
-        <v>44136</v>
+        <v>45047</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -7130,17 +7130,17 @@
         </is>
       </c>
       <c r="D376">
-        <v>15.9021934692295</v>
+        <v>29.76078172247216</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B377" s="2">
-        <v>44166</v>
+        <v>45078</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -7148,17 +7148,17 @@
         </is>
       </c>
       <c r="D377">
-        <v>4.891092955640294</v>
+        <v>4.898584871282273</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B378" s="2">
-        <v>44166</v>
+        <v>45078</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -7166,17 +7166,17 @@
         </is>
       </c>
       <c r="D378">
-        <v>9.49889785581524</v>
+        <v>15.172783509009</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B379" s="2">
-        <v>44166</v>
+        <v>45078</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -7184,17 +7184,17 @@
         </is>
       </c>
       <c r="D379">
-        <v>17.26907863181795</v>
+        <v>29.10494836398669</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B380" s="2">
-        <v>44197</v>
+        <v>45108</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -7202,17 +7202,17 @@
         </is>
       </c>
       <c r="D380">
-        <v>4.060228742985249</v>
+        <v>7.469776872302151</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B381" s="2">
-        <v>44197</v>
+        <v>45108</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -7220,17 +7220,17 @@
         </is>
       </c>
       <c r="D381">
-        <v>8.065244700482808</v>
+        <v>20.19666030709455</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B382" s="2">
-        <v>44197</v>
+        <v>45108</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -7238,17 +7238,17 @@
         </is>
       </c>
       <c r="D382">
-        <v>14.9895167138187</v>
+        <v>30.67618697982102</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B383" s="2">
-        <v>44228</v>
+        <v>45139</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -7256,17 +7256,17 @@
         </is>
       </c>
       <c r="D383">
-        <v>5.0560363568682</v>
+        <v>7.221131170140967</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B384" s="2">
-        <v>44228</v>
+        <v>45139</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -7274,17 +7274,17 @@
         </is>
       </c>
       <c r="D384">
-        <v>9.897395297632837</v>
+        <v>15.79520214039157</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B385" s="2">
-        <v>44228</v>
+        <v>45139</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -7292,17 +7292,17 @@
         </is>
       </c>
       <c r="D385">
-        <v>17.23437859675177</v>
+        <v>27.999984628416</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B386" s="2">
-        <v>44256</v>
+        <v>45170</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -7310,17 +7310,17 @@
         </is>
       </c>
       <c r="D386">
-        <v>4.908885571956795</v>
+        <v>6.64448202515724</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B387" s="2">
-        <v>44256</v>
+        <v>45170</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -7328,17 +7328,17 @@
         </is>
       </c>
       <c r="D387">
-        <v>10.218110263254</v>
+        <v>16.64216816765711</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B388" s="2">
-        <v>44256</v>
+        <v>45170</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -7346,17 +7346,17 @@
         </is>
       </c>
       <c r="D388">
-        <v>19.37799477581197</v>
+        <v>24.61459225859451</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B389" s="2">
-        <v>44287</v>
+        <v>45200</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -7364,17 +7364,17 @@
         </is>
       </c>
       <c r="D389">
-        <v>5.334342549822301</v>
+        <v>5.077393355034868</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B390" s="2">
-        <v>44287</v>
+        <v>45200</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -7382,17 +7382,17 @@
         </is>
       </c>
       <c r="D390">
-        <v>10.89919049570149</v>
+        <v>17.66398261057345</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B391" s="2">
-        <v>44287</v>
+        <v>45200</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -7400,17 +7400,17 @@
         </is>
       </c>
       <c r="D391">
-        <v>19.79869175425435</v>
+        <v>28.87896202617783</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B392" s="2">
-        <v>44317</v>
+        <v>45231</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -7418,17 +7418,17 @@
         </is>
       </c>
       <c r="D392">
-        <v>4.178900386103525</v>
+        <v>7.58048398078404</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B393" s="2">
-        <v>44317</v>
+        <v>45231</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -7436,17 +7436,17 @@
         </is>
       </c>
       <c r="D393">
-        <v>10.41835668210043</v>
+        <v>14.80017743649262</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B394" s="2">
-        <v>44317</v>
+        <v>45231</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -7454,17 +7454,17 @@
         </is>
       </c>
       <c r="D394">
-        <v>20.16504418724712</v>
+        <v>25.34336818075298</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B395" s="2">
-        <v>44348</v>
+        <v>45261</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -7472,17 +7472,17 @@
         </is>
       </c>
       <c r="D395">
-        <v>4.640628111311345</v>
+        <v>6.851729026789424</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B396" s="2">
-        <v>44348</v>
+        <v>45261</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -7490,17 +7490,17 @@
         </is>
       </c>
       <c r="D396">
-        <v>12.02640346854916</v>
+        <v>16.39714659641156</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B397" s="2">
-        <v>44348</v>
+        <v>45261</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -7508,17 +7508,17 @@
         </is>
       </c>
       <c r="D397">
-        <v>22.61948089960124</v>
+        <v>25.41906513992541</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B398" s="2">
-        <v>44378</v>
+        <v>45292</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -7526,17 +7526,17 @@
         </is>
       </c>
       <c r="D398">
-        <v>3.37559563914273</v>
+        <v>5.398531742182316</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B399" s="2">
-        <v>44378</v>
+        <v>45292</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -7544,17 +7544,17 @@
         </is>
       </c>
       <c r="D399">
-        <v>10.97484690431897</v>
+        <v>16.05737375305402</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B400" s="2">
-        <v>44378</v>
+        <v>45292</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -7562,17 +7562,17 @@
         </is>
       </c>
       <c r="D400">
-        <v>18.0278804413023</v>
+        <v>26.96001685106847</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B401" s="2">
-        <v>44409</v>
+        <v>45323</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -7580,17 +7580,17 @@
         </is>
       </c>
       <c r="D401">
-        <v>4.581185277148464</v>
+        <v>7.326688976935341</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B402" s="2">
-        <v>44409</v>
+        <v>45323</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -7598,17 +7598,17 @@
         </is>
       </c>
       <c r="D402">
-        <v>10.81283672770261</v>
+        <v>17.9860648938697</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B403" s="2">
-        <v>44409</v>
+        <v>45323</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -7616,17 +7616,17 @@
         </is>
       </c>
       <c r="D403">
-        <v>17.9935982753604</v>
+        <v>29.44546126068112</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B404" s="2">
-        <v>44440</v>
+        <v>45352</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -7634,17 +7634,17 @@
         </is>
       </c>
       <c r="D404">
-        <v>4.934186690970451</v>
+        <v>7.420786194029754</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B405" s="2">
-        <v>44440</v>
+        <v>45352</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -7652,17 +7652,17 @@
         </is>
       </c>
       <c r="D405">
-        <v>11.22056984272746</v>
+        <v>21.02029652898261</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B406" s="2">
-        <v>44440</v>
+        <v>45352</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -7670,17 +7670,17 @@
         </is>
       </c>
       <c r="D406">
-        <v>19.85849852272626</v>
+        <v>30.30989024248695</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B407" s="2">
-        <v>44470</v>
+        <v>45383</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -7688,17 +7688,17 @@
         </is>
       </c>
       <c r="D407">
-        <v>4.029557112487895</v>
+        <v>6.685398679981517</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B408" s="2">
-        <v>44470</v>
+        <v>45383</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -7706,17 +7706,17 @@
         </is>
       </c>
       <c r="D408">
-        <v>8.639624781724379</v>
+        <v>15.84309056197961</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B409" s="2">
-        <v>44470</v>
+        <v>45383</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -7724,17 +7724,17 @@
         </is>
       </c>
       <c r="D409">
-        <v>17.53347622893255</v>
+        <v>27.79284895603107</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B410" s="2">
-        <v>44501</v>
+        <v>45413</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -7742,17 +7742,17 @@
         </is>
       </c>
       <c r="D410">
-        <v>3.626849610830135</v>
+        <v>3.697760949600832</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B411" s="2">
-        <v>44501</v>
+        <v>45413</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -7760,17 +7760,17 @@
         </is>
       </c>
       <c r="D411">
-        <v>10.50284793374692</v>
+        <v>14.67714767350704</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B412" s="2">
-        <v>44501</v>
+        <v>45413</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -7778,17 +7778,17 @@
         </is>
       </c>
       <c r="D412">
-        <v>20.59632101378336</v>
+        <v>25.51328551570763</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B413" s="2">
-        <v>44531</v>
+        <v>45444</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -7796,17 +7796,17 @@
         </is>
       </c>
       <c r="D413">
-        <v>4.294500614144154</v>
+        <v>6.823322954151708</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B414" s="2">
-        <v>44531</v>
+        <v>45444</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -7814,17 +7814,17 @@
         </is>
       </c>
       <c r="D414">
-        <v>11.52484868635352</v>
+        <v>14.59723458836907</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B415" s="2">
-        <v>44531</v>
+        <v>45444</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -7832,17 +7832,17 @@
         </is>
       </c>
       <c r="D415">
-        <v>20.53230790122646</v>
+        <v>28.19515894079646</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B416" s="2">
-        <v>44562</v>
+        <v>45474</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -7850,17 +7850,17 @@
         </is>
       </c>
       <c r="D416">
-        <v>6.402419533311106</v>
+        <v>5.984690430321632</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B417" s="2">
-        <v>44562</v>
+        <v>45474</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -7868,17 +7868,17 @@
         </is>
       </c>
       <c r="D417">
-        <v>15.10356602455456</v>
+        <v>14.21554806118263</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B418" s="2">
-        <v>44562</v>
+        <v>45474</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -7886,17 +7886,17 @@
         </is>
       </c>
       <c r="D418">
-        <v>23.54727035881082</v>
+        <v>26.80990340323754</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B419" s="2">
-        <v>44593</v>
+        <v>45505</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -7904,17 +7904,17 @@
         </is>
       </c>
       <c r="D419">
-        <v>3.807412917690085</v>
+        <v>4.36869678541356</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B420" s="2">
-        <v>44593</v>
+        <v>45505</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -7922,17 +7922,17 @@
         </is>
       </c>
       <c r="D420">
-        <v>11.16547803886123</v>
+        <v>14.62747987880348</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B421" s="2">
-        <v>44593</v>
+        <v>45505</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -7940,17 +7940,17 @@
         </is>
       </c>
       <c r="D421">
-        <v>20.06697707390957</v>
+        <v>26.61560877109147</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B422" s="2">
-        <v>44621</v>
+        <v>45536</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -7958,17 +7958,17 @@
         </is>
       </c>
       <c r="D422">
-        <v>4.587460076341372</v>
+        <v>6.242355239895647</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B423" s="2">
-        <v>44621</v>
+        <v>45536</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -7976,17 +7976,17 @@
         </is>
       </c>
       <c r="D423">
-        <v>11.08242109863186</v>
+        <v>14.35606087876745</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B424" s="2">
-        <v>44621</v>
+        <v>45536</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -7994,17 +7994,17 @@
         </is>
       </c>
       <c r="D424">
-        <v>19.94577435339493</v>
+        <v>24.92587263160031</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B425" s="2">
-        <v>44652</v>
+        <v>45566</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -8012,17 +8012,17 @@
         </is>
       </c>
       <c r="D425">
-        <v>3.831594574036286</v>
+        <v>6.553544091982802</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B426" s="2">
-        <v>44652</v>
+        <v>45566</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -8030,17 +8030,17 @@
         </is>
       </c>
       <c r="D426">
-        <v>11.07376278420784</v>
+        <v>15.2829467893346</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B427" s="2">
-        <v>44652</v>
+        <v>45566</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -8048,17 +8048,17 @@
         </is>
       </c>
       <c r="D427">
-        <v>16.91477925129175</v>
+        <v>26.98819231594014</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B428" s="2">
-        <v>44682</v>
+        <v>45597</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -8066,17 +8066,17 @@
         </is>
       </c>
       <c r="D428">
-        <v>3.950260446787136</v>
+        <v>3.21885960311939</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B429" s="2">
-        <v>44682</v>
+        <v>45597</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -8084,17 +8084,17 @@
         </is>
       </c>
       <c r="D429">
-        <v>11.33701904348944</v>
+        <v>11.13890776325891</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B430" s="2">
-        <v>44682</v>
+        <v>45597</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -8102,17 +8102,17 @@
         </is>
       </c>
       <c r="D430">
-        <v>22.44307622652039</v>
+        <v>21.99022531934232</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B431" s="2">
-        <v>44713</v>
+        <v>45627</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -8120,17 +8120,17 @@
         </is>
       </c>
       <c r="D431">
-        <v>3.043680077718839</v>
+        <v>6.072974963685712</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B432" s="2">
-        <v>44713</v>
+        <v>45627</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -8138,17 +8138,17 @@
         </is>
       </c>
       <c r="D432">
-        <v>10.28908648916008</v>
+        <v>13.89743662161426</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B433" s="2">
-        <v>44713</v>
+        <v>45627</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="D433">
-        <v>22.82209788964152</v>
+        <v>25.22905945512906</v>
       </c>
     </row>
     <row r="434">
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="B434" s="2">
-        <v>44743</v>
+        <v>43466</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="D434">
-        <v>5.023588352581966</v>
+        <v>3.6349493549969</v>
       </c>
     </row>
     <row r="435">
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="B435" s="2">
-        <v>44743</v>
+        <v>43466</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="D435">
-        <v>10.99161160927578</v>
+        <v>10.11050115125111</v>
       </c>
     </row>
     <row r="436">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="B436" s="2">
-        <v>44743</v>
+        <v>43466</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="D436">
-        <v>22.22886093002493</v>
+        <v>16.42017499049537</v>
       </c>
     </row>
     <row r="437">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="B437" s="2">
-        <v>44774</v>
+        <v>43497</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="D437">
-        <v>4.161074627852384</v>
+        <v>3.977230540665857</v>
       </c>
     </row>
     <row r="438">
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="B438" s="2">
-        <v>44774</v>
+        <v>43497</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="D438">
-        <v>10.45896734458771</v>
+        <v>8.238228207578885</v>
       </c>
     </row>
     <row r="439">
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="B439" s="2">
-        <v>44774</v>
+        <v>43497</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="D439">
-        <v>17.74170114596155</v>
+        <v>15.42942871566926</v>
       </c>
     </row>
     <row r="440">
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="B440" s="2">
-        <v>44805</v>
+        <v>43525</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="D440">
-        <v>3.492168139204651</v>
+        <v>3.425208838612741</v>
       </c>
     </row>
     <row r="441">
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B441" s="2">
-        <v>44805</v>
+        <v>43525</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="D441">
-        <v>9.712740625035334</v>
+        <v>8.026509093648716</v>
       </c>
     </row>
     <row r="442">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="B442" s="2">
-        <v>44805</v>
+        <v>43525</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="D442">
-        <v>19.16846163399564</v>
+        <v>13.83632104810355</v>
       </c>
     </row>
     <row r="443">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="B443" s="2">
-        <v>44835</v>
+        <v>43556</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="D443">
-        <v>3.700555753989561</v>
+        <v>3.218378908891774</v>
       </c>
     </row>
     <row r="444">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="B444" s="2">
-        <v>44835</v>
+        <v>43556</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="D444">
-        <v>9.123522035509444</v>
+        <v>7.866500759283099</v>
       </c>
     </row>
     <row r="445">
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B445" s="2">
-        <v>44835</v>
+        <v>43556</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="D445">
-        <v>18.015661777063</v>
+        <v>13.23195813812105</v>
       </c>
     </row>
     <row r="446">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B446" s="2">
-        <v>44866</v>
+        <v>43586</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="D446">
-        <v>5.160821671864942</v>
+        <v>3.766302624944184</v>
       </c>
     </row>
     <row r="447">
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="B447" s="2">
-        <v>44866</v>
+        <v>43586</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="D447">
-        <v>10.95852161714424</v>
+        <v>7.634820589984834</v>
       </c>
     </row>
     <row r="448">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="B448" s="2">
-        <v>44866</v>
+        <v>43586</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="D448">
-        <v>22.60274102149944</v>
+        <v>14.04745597323936</v>
       </c>
     </row>
     <row r="449">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="B449" s="2">
-        <v>44896</v>
+        <v>43617</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="D449">
-        <v>3.843117770882819</v>
+        <v>3.458306529438883</v>
       </c>
     </row>
     <row r="450">
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="B450" s="2">
-        <v>44896</v>
+        <v>43617</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="D450">
-        <v>10.95357752799289</v>
+        <v>6.710999456412623</v>
       </c>
     </row>
     <row r="451">
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="B451" s="2">
-        <v>44896</v>
+        <v>43617</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="D451">
-        <v>24.7202568930232</v>
+        <v>12.28850060630379</v>
       </c>
     </row>
     <row r="452">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B452" s="2">
-        <v>44927</v>
+        <v>43647</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="D452">
-        <v>6.722795450765901</v>
+        <v>3.128694008579072</v>
       </c>
     </row>
     <row r="453">
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="B453" s="2">
-        <v>44927</v>
+        <v>43647</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="D453">
-        <v>15.20717333984185</v>
+        <v>7.225202870356553</v>
       </c>
     </row>
     <row r="454">
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B454" s="2">
-        <v>44927</v>
+        <v>43647</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="D454">
-        <v>25.9091822005293</v>
+        <v>12.82281884062744</v>
       </c>
     </row>
     <row r="455">
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B455" s="2">
-        <v>44958</v>
+        <v>43678</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="D455">
-        <v>6.477665053242314</v>
+        <v>3.536389176905308</v>
       </c>
     </row>
     <row r="456">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="B456" s="2">
-        <v>44958</v>
+        <v>43678</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="D456">
-        <v>14.33858321675414</v>
+        <v>7.064997935219369</v>
       </c>
     </row>
     <row r="457">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B457" s="2">
-        <v>44958</v>
+        <v>43678</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="D457">
-        <v>24.9722818531918</v>
+        <v>11.19374909605078</v>
       </c>
     </row>
     <row r="458">
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="B458" s="2">
-        <v>44986</v>
+        <v>43709</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="D458">
-        <v>8.467230111083675</v>
+        <v>3.517101731044673</v>
       </c>
     </row>
     <row r="459">
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B459" s="2">
-        <v>44986</v>
+        <v>43709</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="D459">
-        <v>17.70081523186025</v>
+        <v>7.450481302466693</v>
       </c>
     </row>
     <row r="460">
@@ -8634,15 +8634,3417 @@
         </is>
       </c>
       <c r="B460" s="2">
+        <v>43709</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D460">
+        <v>13.70987075558255</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B461" s="2">
+        <v>43739</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D461">
+        <v>2.44455895400372</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B462" s="2">
+        <v>43739</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D462">
+        <v>5.216849297711635</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B463" s="2">
+        <v>43739</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D463">
+        <v>11.40182503458006</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B464" s="2">
+        <v>43770</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D464">
+        <v>2.531755231569268</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B465" s="2">
+        <v>43770</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D465">
+        <v>5.541244937880761</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B466" s="2">
+        <v>43770</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D466">
+        <v>11.67915398099378</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B467" s="2">
+        <v>43800</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D467">
+        <v>4.03390565677894</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B468" s="2">
+        <v>43800</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D468">
+        <v>7.082203851823957</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B469" s="2">
+        <v>43800</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D469">
+        <v>14.33674175848242</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B470" s="2">
+        <v>43831</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D470">
+        <v>2.81015544718536</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B471" s="2">
+        <v>43831</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D471">
+        <v>5.574891248144008</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B472" s="2">
+        <v>43831</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D472">
+        <v>10.21530757732704</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B473" s="2">
+        <v>43862</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D473">
+        <v>4.165757989575734</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B474" s="2">
+        <v>43862</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D474">
+        <v>8.211029338959245</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B475" s="2">
+        <v>43862</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D475">
+        <v>13.67698510560965</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B476" s="2">
+        <v>43891</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D476">
+        <v>8.007656954473042</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B477" s="2">
+        <v>43891</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D477">
+        <v>13.2793373091607</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B478" s="2">
+        <v>43891</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D478">
+        <v>19.0099697292832</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B479" s="2">
+        <v>43922</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D479">
+        <v>14.65089536566943</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B480" s="2">
+        <v>43922</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D480">
+        <v>22.85772977244308</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B481" s="2">
+        <v>43922</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D481">
+        <v>34.64756870116229</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B482" s="2">
+        <v>43952</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D482">
+        <v>18.65634538780538</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B483" s="2">
+        <v>43952</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D483">
+        <v>27.84260654062342</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B484" s="2">
+        <v>43952</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D484">
+        <v>38.93451674663208</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B485" s="2">
+        <v>43983</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D485">
+        <v>16.77730646300213</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B486" s="2">
+        <v>43983</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D486">
+        <v>27.04594074295498</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B487" s="2">
+        <v>43983</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D487">
+        <v>37.3933252883466</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B488" s="2">
+        <v>44013</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D488">
+        <v>14.69866124001517</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B489" s="2">
+        <v>44013</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D489">
+        <v>23.6845758843451</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B490" s="2">
+        <v>44013</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D490">
+        <v>34.79729326724932</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B491" s="2">
+        <v>44044</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D491">
+        <v>10.28042905307037</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B492" s="2">
+        <v>44044</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D492">
+        <v>17.70557193198582</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B493" s="2">
+        <v>44044</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D493">
+        <v>29.00573638579855</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B494" s="2">
+        <v>44075</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D494">
+        <v>6.474743825349387</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B495" s="2">
+        <v>44075</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D495">
+        <v>12.96943714885955</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B496" s="2">
+        <v>44075</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D496">
+        <v>21.69657673954115</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B497" s="2">
+        <v>44105</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D497">
+        <v>4.873547040611218</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B498" s="2">
+        <v>44105</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D498">
+        <v>12.16941138926549</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B499" s="2">
+        <v>44105</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D499">
+        <v>19.29075592179443</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B500" s="2">
+        <v>44136</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D500">
+        <v>5.441884722788836</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B501" s="2">
+        <v>44136</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D501">
+        <v>9.104773457233595</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B502" s="2">
+        <v>44136</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D502">
+        <v>15.9021934692295</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B503" s="2">
+        <v>44166</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D503">
+        <v>4.891092955640294</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B504" s="2">
+        <v>44166</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D504">
+        <v>9.49889785581524</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B505" s="2">
+        <v>44166</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D505">
+        <v>17.26907863181795</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B506" s="2">
+        <v>44197</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D506">
+        <v>4.060228742985249</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B507" s="2">
+        <v>44197</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D507">
+        <v>8.065244700482808</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B508" s="2">
+        <v>44197</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D508">
+        <v>14.9895167138187</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B509" s="2">
+        <v>44228</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D509">
+        <v>5.0560363568682</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B510" s="2">
+        <v>44228</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D510">
+        <v>9.897395297632837</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B511" s="2">
+        <v>44228</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D511">
+        <v>17.23437859675177</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B512" s="2">
+        <v>44256</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D512">
+        <v>4.908885571956795</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B513" s="2">
+        <v>44256</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D513">
+        <v>10.218110263254</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B514" s="2">
+        <v>44256</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D514">
+        <v>19.37799477581197</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B515" s="2">
+        <v>44287</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D515">
+        <v>5.334342549822301</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B516" s="2">
+        <v>44287</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D516">
+        <v>10.89919049570149</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B517" s="2">
+        <v>44287</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D517">
+        <v>19.79869175425435</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B518" s="2">
+        <v>44317</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D518">
+        <v>4.178900386103525</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B519" s="2">
+        <v>44317</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D519">
+        <v>10.41835668210043</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B520" s="2">
+        <v>44317</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D520">
+        <v>20.16504418724712</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B521" s="2">
+        <v>44348</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D521">
+        <v>4.640628111311345</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B522" s="2">
+        <v>44348</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D522">
+        <v>12.02640346854916</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B523" s="2">
+        <v>44348</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D523">
+        <v>22.61948089960124</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B524" s="2">
+        <v>44378</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D524">
+        <v>3.37559563914273</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B525" s="2">
+        <v>44378</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D525">
+        <v>10.97484690431897</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B526" s="2">
+        <v>44378</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D526">
+        <v>18.0278804413023</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B527" s="2">
+        <v>44409</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D527">
+        <v>4.581185277148464</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B528" s="2">
+        <v>44409</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D528">
+        <v>10.81283672770261</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B529" s="2">
+        <v>44409</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D529">
+        <v>17.9935982753604</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B530" s="2">
+        <v>44440</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D530">
+        <v>4.934186690970451</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B531" s="2">
+        <v>44440</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D531">
+        <v>11.22056984272746</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B532" s="2">
+        <v>44440</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D532">
+        <v>19.85849852272626</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B533" s="2">
+        <v>44470</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D533">
+        <v>4.029557112487895</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B534" s="2">
+        <v>44470</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D534">
+        <v>8.639624781724379</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B535" s="2">
+        <v>44470</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D535">
+        <v>17.53347622893255</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B536" s="2">
+        <v>44501</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D536">
+        <v>3.626849610830135</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B537" s="2">
+        <v>44501</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D537">
+        <v>10.50284793374692</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B538" s="2">
+        <v>44501</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D538">
+        <v>20.59632101378336</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B539" s="2">
+        <v>44531</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D539">
+        <v>4.294500614144154</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B540" s="2">
+        <v>44531</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D540">
+        <v>11.52484868635352</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B541" s="2">
+        <v>44531</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D541">
+        <v>20.53230790122646</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B542" s="2">
+        <v>44562</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D542">
+        <v>6.402419533311106</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B543" s="2">
+        <v>44562</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D543">
+        <v>15.10356602455456</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B544" s="2">
+        <v>44562</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D544">
+        <v>23.54727035881082</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B545" s="2">
+        <v>44593</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D545">
+        <v>3.807412917690085</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B546" s="2">
+        <v>44593</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D546">
+        <v>11.16547803886123</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B547" s="2">
+        <v>44593</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D547">
+        <v>20.06697707390957</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B548" s="2">
+        <v>44621</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D548">
+        <v>4.587460076341372</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B549" s="2">
+        <v>44621</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D549">
+        <v>11.08242109863186</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B550" s="2">
+        <v>44621</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D550">
+        <v>19.94577435339493</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B551" s="2">
+        <v>44652</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D551">
+        <v>3.831594574036286</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B552" s="2">
+        <v>44652</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D552">
+        <v>11.07376278420784</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B553" s="2">
+        <v>44652</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D553">
+        <v>16.91477925129175</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B554" s="2">
+        <v>44682</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D554">
+        <v>3.950260446787136</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B555" s="2">
+        <v>44682</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D555">
+        <v>11.33701904348944</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B556" s="2">
+        <v>44682</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D556">
+        <v>22.44307622652039</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B557" s="2">
+        <v>44713</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D557">
+        <v>3.043680077718839</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B558" s="2">
+        <v>44713</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D558">
+        <v>10.28908648916008</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B559" s="2">
+        <v>44713</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D559">
+        <v>22.82209788964152</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B560" s="2">
+        <v>44743</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D560">
+        <v>5.023588352581966</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B561" s="2">
+        <v>44743</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D561">
+        <v>10.99161160927578</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B562" s="2">
+        <v>44743</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D562">
+        <v>22.22886093002493</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B563" s="2">
+        <v>44774</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D563">
+        <v>4.161074627852384</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B564" s="2">
+        <v>44774</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D564">
+        <v>10.45896734458771</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B565" s="2">
+        <v>44774</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D565">
+        <v>17.74170114596155</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B566" s="2">
+        <v>44805</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D566">
+        <v>3.492168139204651</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B567" s="2">
+        <v>44805</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D567">
+        <v>9.712740625035334</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B568" s="2">
+        <v>44805</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D568">
+        <v>19.16846163399564</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B569" s="2">
+        <v>44835</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D569">
+        <v>3.700555753989561</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B570" s="2">
+        <v>44835</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D570">
+        <v>9.123522035509444</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B571" s="2">
+        <v>44835</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D571">
+        <v>18.015661777063</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B572" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D572">
+        <v>5.160821671864942</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B573" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D573">
+        <v>10.95852161714424</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B574" s="2">
+        <v>44866</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D574">
+        <v>22.60274102149944</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B575" s="2">
+        <v>44896</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D575">
+        <v>3.843117770882819</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B576" s="2">
+        <v>44896</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D576">
+        <v>10.95357752799289</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B577" s="2">
+        <v>44896</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D577">
+        <v>24.7202568930232</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B578" s="2">
+        <v>44927</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D578">
+        <v>6.722795450765901</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B579" s="2">
+        <v>44927</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D579">
+        <v>15.20717333984185</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B580" s="2">
+        <v>44927</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D580">
+        <v>25.9091822005293</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B581" s="2">
+        <v>44958</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D581">
+        <v>6.477665053242314</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B582" s="2">
+        <v>44958</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D582">
+        <v>14.33858321675414</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B583" s="2">
+        <v>44958</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D583">
+        <v>24.9722818531918</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B584" s="2">
         <v>44986</v>
       </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>CoRD</t>
-        </is>
-      </c>
-      <c r="D460">
-        <v>30.27804662788404</v>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D584">
+        <v>7.477679044063744</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B585" s="2">
+        <v>44986</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D585">
+        <v>15.51069736611189</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B586" s="2">
+        <v>44986</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D586">
+        <v>26.63393248290625</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B587" s="2">
+        <v>45017</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D587">
+        <v>6.79795945503935</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B588" s="2">
+        <v>45017</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D588">
+        <v>14.09542280858739</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B589" s="2">
+        <v>45017</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D589">
+        <v>24.37060827874872</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B590" s="2">
+        <v>45047</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D590">
+        <v>5.160349489126444</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B591" s="2">
+        <v>45047</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D591">
+        <v>12.77783505627143</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B592" s="2">
+        <v>45047</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D592">
+        <v>23.58581741824217</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B593" s="2">
+        <v>45078</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D593">
+        <v>3.826052727396883</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B594" s="2">
+        <v>45078</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D594">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B595" s="2">
+        <v>45078</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D595">
+        <v>15.97755789902416</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B596" s="2">
+        <v>45108</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D596">
+        <v>3.348694654995864</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B597" s="2">
+        <v>45108</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D597">
+        <v>8.759006940765683</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B598" s="2">
+        <v>45108</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D598">
+        <v>16.4180142361205</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B599" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D599">
+        <v>3.437897827121065</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B600" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D600">
+        <v>9.874513926949152</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B601" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D601">
+        <v>16.82583460755778</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B602" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D602">
+        <v>2.768335507010574</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B603" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D603">
+        <v>7.996071069541896</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B604" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D604">
+        <v>15.75140763084564</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B605" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D605">
+        <v>3.047648483191709</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B606" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D606">
+        <v>7.481725450313471</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B607" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D607">
+        <v>12.48257861737416</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B608" s="2">
+        <v>45231</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D608">
+        <v>5.035966741843255</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B609" s="2">
+        <v>45231</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D609">
+        <v>12.71321345966379</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B610" s="2">
+        <v>45231</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D610">
+        <v>19.40467283886249</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B611" s="2">
+        <v>45261</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D611">
+        <v>3.991374522601242</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B612" s="2">
+        <v>45261</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D612">
+        <v>9.1645997448333</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B613" s="2">
+        <v>45261</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D613">
+        <v>15.37814243419857</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B614" s="2">
+        <v>45292</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D614">
+        <v>4.913115377020018</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B615" s="2">
+        <v>45292</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D615">
+        <v>11.76283482394936</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B616" s="2">
+        <v>45292</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D616">
+        <v>18.28713940138992</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B617" s="2">
+        <v>45323</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D617">
+        <v>5.363270098697538</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B618" s="2">
+        <v>45323</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D618">
+        <v>11.06434219652243</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B619" s="2">
+        <v>45323</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D619">
+        <v>17.36401263645125</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B620" s="2">
+        <v>45352</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D620">
+        <v>2.372819070941788</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B621" s="2">
+        <v>45352</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D621">
+        <v>7.438510922830633</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B622" s="2">
+        <v>45352</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D622">
+        <v>14.23097393160469</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B623" s="2">
+        <v>45383</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D623">
+        <v>3.717891317284637</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B624" s="2">
+        <v>45383</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D624">
+        <v>10.32784902024128</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B625" s="2">
+        <v>45383</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D625">
+        <v>16.81260506313956</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B626" s="2">
+        <v>45413</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D626">
+        <v>3.213840850726551</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B627" s="2">
+        <v>45413</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D627">
+        <v>9.89358449901238</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B628" s="2">
+        <v>45413</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D628">
+        <v>16.12947381696675</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B629" s="2">
+        <v>45444</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D629">
+        <v>2.776513196622282</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B630" s="2">
+        <v>45444</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D630">
+        <v>9.151792376668194</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B631" s="2">
+        <v>45444</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D631">
+        <v>17.20229100166409</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B632" s="2">
+        <v>45474</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D632">
+        <v>2.436267182060473</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B633" s="2">
+        <v>45474</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D633">
+        <v>7.45253074588901</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B634" s="2">
+        <v>45474</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D634">
+        <v>13.26110759137072</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B635" s="2">
+        <v>45505</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D635">
+        <v>2.319129459993856</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B636" s="2">
+        <v>45505</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D636">
+        <v>7.794805005521715</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B637" s="2">
+        <v>45505</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D637">
+        <v>11.82315349537567</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B638" s="2">
+        <v>45536</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D638">
+        <v>2.015387776464054</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B639" s="2">
+        <v>45536</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D639">
+        <v>6.258816775679988</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B640" s="2">
+        <v>45536</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D640">
+        <v>11.08244217676061</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B641" s="2">
+        <v>45566</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D641">
+        <v>1.723627294301786</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B642" s="2">
+        <v>45566</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D642">
+        <v>5.961400012471701</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B643" s="2">
+        <v>45566</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D643">
+        <v>10.16328541796411</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B644" s="2">
+        <v>45597</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D644">
+        <v>1.849215247642079</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B645" s="2">
+        <v>45597</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D645">
+        <v>6.11634020041302</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B646" s="2">
+        <v>45597</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D646">
+        <v>12.95495244625456</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B647" s="2">
+        <v>45627</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>CoCA</t>
+        </is>
+      </c>
+      <c r="D647">
+        <v>1.983549978164193</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B648" s="2">
+        <v>45627</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>CoNA</t>
+        </is>
+      </c>
+      <c r="D648">
+        <v>6.362740947171663</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B649" s="2">
+        <v>45627</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>CoRD</t>
+        </is>
+      </c>
+      <c r="D649">
+        <v>12.39659047416784</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
+++ b/Proyecto Interno/food-security-paper/output/figures/fig_afford_overall_rate.xlsx
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>6.472932673522782</v>
+        <v>6.796960123642282</v>
       </c>
     </row>
     <row r="13">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>5.501025360264888</v>
+        <v>5.63630184986604</v>
       </c>
     </row>
     <row r="16">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>6.779579213330199</v>
+        <v>7.046998441740985</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>7.52853771461441</v>
+        <v>7.636494348913809</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>6.797287195943042</v>
+        <v>7.124722045141716</v>
       </c>
     </row>
     <row r="40">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>12.68310153318386</v>
+        <v>13.1043633177434</v>
       </c>
     </row>
     <row r="46">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>33.85572043362379</v>
+        <v>34.34579026798712</v>
       </c>
     </row>
     <row r="52">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>31.10884899552155</v>
+        <v>31.21781760871128</v>
       </c>
     </row>
     <row r="55">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>30.35842528260586</v>
+        <v>30.56012100076455</v>
       </c>
     </row>
     <row r="58">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="D60">
-        <v>15.83424008160425</v>
+        <v>16.18554282222601</v>
       </c>
     </row>
     <row r="61">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>16.36923957365472</v>
+        <v>16.45641495943078</v>
       </c>
     </row>
     <row r="64">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>12.39234410302949</v>
+        <v>13.2088521466806</v>
       </c>
     </row>
     <row r="67">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>10.64745612530219</v>
+        <v>11.16839730761196</v>
       </c>
     </row>
     <row r="70">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>14.06448569007672</v>
+        <v>14.29246208339874</v>
       </c>
     </row>
     <row r="73">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="D78">
-        <v>12.7554371644127</v>
+        <v>13.14756649575848</v>
       </c>
     </row>
     <row r="79">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>14.26077482253129</v>
+        <v>14.42306530822419</v>
       </c>
     </row>
     <row r="82">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>16.15527563270406</v>
+        <v>16.25577640383314</v>
       </c>
     </row>
     <row r="85">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>14.61627297860222</v>
+        <v>14.87979845848897</v>
       </c>
     </row>
     <row r="88">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>15.26851188386701</v>
+        <v>15.53203851314017</v>
       </c>
     </row>
     <row r="91">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>12.2243276496713</v>
+        <v>12.72860070744581</v>
       </c>
     </row>
     <row r="94">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>12.92235967052276</v>
+        <v>13.01370434002478</v>
       </c>
     </row>
     <row r="97">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>10.84171340267484</v>
+        <v>11.00392909010874</v>
       </c>
     </row>
     <row r="106">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="D111">
-        <v>11.78432108213274</v>
+        <v>12.19602253456409</v>
       </c>
     </row>
     <row r="112">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="D114">
-        <v>12.22175816757322</v>
+        <v>12.32435117563491</v>
       </c>
     </row>
     <row r="115">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="D117">
-        <v>10.81592954097202</v>
+        <v>11.03760421086593</v>
       </c>
     </row>
     <row r="118">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>12.68195461690708</v>
+        <v>12.83170136169793</v>
       </c>
     </row>
     <row r="121">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>11.9186273534628</v>
+        <v>12.21895960912595</v>
       </c>
     </row>
     <row r="127">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>13.00259698603256</v>
+        <v>13.39698993512376</v>
       </c>
     </row>
     <row r="130">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>11.43356520489169</v>
+        <v>11.64514470352387</v>
       </c>
     </row>
     <row r="133">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>14.17552334534968</v>
+        <v>14.3420508925557</v>
       </c>
     </row>
     <row r="139">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>11.39467215673453</v>
+        <v>11.51368860906837</v>
       </c>
     </row>
     <row r="145">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>12.91183754948726</v>
+        <v>13.25557931586254</v>
       </c>
     </row>
     <row r="151">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>12.10609146102434</v>
+        <v>12.16899636962724</v>
       </c>
     </row>
     <row r="154">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>11.50619313963423</v>
+        <v>11.62234856862248</v>
       </c>
     </row>
     <row r="157">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>11.83819342886537</v>
+        <v>12.02174989023315</v>
       </c>
     </row>
     <row r="160">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>11.08834799079342</v>
+        <v>11.63144482527954</v>
       </c>
     </row>
     <row r="163">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>11.18637044530531</v>
+        <v>11.297214401296</v>
       </c>
     </row>
     <row r="169">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>8.712244749991834</v>
+        <v>8.959883747772885</v>
       </c>
     </row>
     <row r="172">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>10.69391685325569</v>
+        <v>10.83072668940277</v>
       </c>
     </row>
     <row r="175">
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>8.019353536894723</v>
+        <v>8.108377938727056</v>
       </c>
     </row>
     <row r="178">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>11.65099245490214</v>
+        <v>11.71784458183482</v>
       </c>
     </row>
     <row r="181">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>9.466203472610394</v>
+        <v>9.559571628257087</v>
       </c>
     </row>
     <row r="184">
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>9.746929318372372</v>
+        <v>9.818207490806286</v>
       </c>
     </row>
     <row r="187">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>6.72642579865734</v>
+        <v>6.892871864051526</v>
       </c>
     </row>
     <row r="190">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>8.235936051110492</v>
+        <v>8.361465485198419</v>
       </c>
     </row>
     <row r="226">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>8.949504834993757</v>
+        <v>9.26002830837643</v>
       </c>
     </row>
     <row r="229">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>7.869762218194597</v>
+        <v>8.174605962575944</v>
       </c>
     </row>
     <row r="235">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>7.282801826068171</v>
+        <v>7.431580577871864</v>
       </c>
     </row>
     <row r="238">
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>6.486997236306701</v>
+        <v>6.902675550545773</v>
       </c>
     </row>
     <row r="241">
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>10.21727871051709</v>
+        <v>10.30654816292301</v>
       </c>
     </row>
     <row r="250">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>9.497517174436883</v>
+        <v>9.672530566756809</v>
       </c>
     </row>
     <row r="256">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D258">
-        <v>6.96552905058366</v>
+        <v>7.187288646349397</v>
       </c>
     </row>
     <row r="259">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="D267">
-        <v>38.19373089771111</v>
+        <v>38.50119430151062</v>
       </c>
     </row>
     <row r="268">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="D273">
-        <v>32.1511019488425</v>
+        <v>32.95541856713527</v>
       </c>
     </row>
     <row r="274">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D276">
-        <v>19.20141585249397</v>
+        <v>19.32858253875237</v>
       </c>
     </row>
     <row r="277">
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>14.76466615963838</v>
+        <v>14.99025669049897</v>
       </c>
     </row>
     <row r="283">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>11.47174402640319</v>
+        <v>12.28827266596819</v>
       </c>
     </row>
     <row r="286">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="D288">
-        <v>11.95383968314153</v>
+        <v>12.60178948120511</v>
       </c>
     </row>
     <row r="289">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="D291">
-        <v>12.75839874800015</v>
+        <v>13.36156542287232</v>
       </c>
     </row>
     <row r="292">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="D294">
-        <v>12.29688385478446</v>
+        <v>12.71715207948011</v>
       </c>
     </row>
     <row r="295">
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="D303">
-        <v>19.29812718502892</v>
+        <v>19.42389678933441</v>
       </c>
     </row>
     <row r="304">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="D306">
-        <v>17.33301201115656</v>
+        <v>17.78388111360317</v>
       </c>
     </row>
     <row r="307">
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="D309">
-        <v>12.7488034454403</v>
+        <v>12.97778800272124</v>
       </c>
     </row>
     <row r="310">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="D312">
-        <v>11.86231183874567</v>
+        <v>12.59517765521377</v>
       </c>
     </row>
     <row r="313">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="D324">
-        <v>11.55527915565783</v>
+        <v>11.8193410460571</v>
       </c>
     </row>
     <row r="325">
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="D330">
-        <v>14.62757879511282</v>
+        <v>15.14136573949396</v>
       </c>
     </row>
     <row r="331">
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="D333">
-        <v>12.0618334226017</v>
+        <v>12.61223173229166</v>
       </c>
     </row>
     <row r="334">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="D336">
-        <v>10</v>
+        <v>10.32137462257661</v>
       </c>
     </row>
     <row r="337">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="D339">
-        <v>12.39391008263184</v>
+        <v>12.57573611260265</v>
       </c>
     </row>
     <row r="340">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="D342">
-        <v>13.42662363267418</v>
+        <v>13.44626193488023</v>
       </c>
     </row>
     <row r="343">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D345">
-        <v>14.70783525380426</v>
+        <v>14.93869628524741</v>
       </c>
     </row>
     <row r="346">
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="D348">
-        <v>13.47970289847173</v>
+        <v>13.61610558734176</v>
       </c>
     </row>
     <row r="349">
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="D351">
-        <v>13.99874069065162</v>
+        <v>14.22756470500589</v>
       </c>
     </row>
     <row r="352">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="D354">
-        <v>11.31250897362911</v>
+        <v>11.32923417159801</v>
       </c>
     </row>
     <row r="355">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="D357">
-        <v>13.78237899001062</v>
+        <v>13.96813491184767</v>
       </c>
     </row>
     <row r="358">
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="D360">
-        <v>14.46429996756167</v>
+        <v>14.62275319194347</v>
       </c>
     </row>
     <row r="361">
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="D363">
-        <v>18.25116173820857</v>
+        <v>18.36537025946117</v>
       </c>
     </row>
     <row r="364">
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="D369">
-        <v>19.66228489123335</v>
+        <v>20.45016340843489</v>
       </c>
     </row>
     <row r="370">
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="D372">
-        <v>17.24405480393601</v>
+        <v>17.36858828484784</v>
       </c>
     </row>
     <row r="373">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="D375">
-        <v>15.95363274769398</v>
+        <v>15.96451971329397</v>
       </c>
     </row>
     <row r="376">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="D381">
-        <v>20.19666030709455</v>
+        <v>20.31349832584921</v>
       </c>
     </row>
     <row r="382">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="D384">
-        <v>15.79520214039157</v>
+        <v>15.87735201551421</v>
       </c>
     </row>
     <row r="385">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D387">
-        <v>16.64216816765711</v>
+        <v>16.77689136736703</v>
       </c>
     </row>
     <row r="388">
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="D393">
-        <v>14.80017743649262</v>
+        <v>14.91845434786666</v>
       </c>
     </row>
     <row r="394">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="D396">
-        <v>16.39714659641156</v>
+        <v>16.57549635734837</v>
       </c>
     </row>
     <row r="397">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="D432">
-        <v>13.89743662161426</v>
+        <v>14.10657051024447</v>
       </c>
     </row>
     <row r="433">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="D435">
-        <v>10.11050115125111</v>
+        <v>10.20508101837421</v>
       </c>
     </row>
     <row r="436">
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="D438">
-        <v>8.238228207578885</v>
+        <v>8.506208686917079</v>
       </c>
     </row>
     <row r="439">
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="D441">
-        <v>8.026509093648716</v>
+        <v>8.207297299854421</v>
       </c>
     </row>
     <row r="442">
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="D450">
-        <v>6.710999456412623</v>
+        <v>7.077234728305636</v>
       </c>
     </row>
     <row r="451">
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="D453">
-        <v>7.225202870356553</v>
+        <v>7.308983847327303</v>
       </c>
     </row>
     <row r="454">
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="D456">
-        <v>7.064997935219369</v>
+        <v>7.136448976969963</v>
       </c>
     </row>
     <row r="457">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="D459">
-        <v>7.450481302466693</v>
+        <v>7.552724190848508</v>
       </c>
     </row>
     <row r="460">
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="D471">
-        <v>5.574891248144008</v>
+        <v>5.673160879141415</v>
       </c>
     </row>
     <row r="472">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="D474">
-        <v>8.211029338959245</v>
+        <v>8.275227427172407</v>
       </c>
     </row>
     <row r="475">
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="D477">
-        <v>13.2793373091607</v>
+        <v>13.34187642244854</v>
       </c>
     </row>
     <row r="478">
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="D480">
-        <v>22.85772977244308</v>
+        <v>23.06211024374458</v>
       </c>
     </row>
     <row r="481">
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="D486">
-        <v>27.04594074295498</v>
+        <v>27.58431393984301</v>
       </c>
     </row>
     <row r="487">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="D492">
-        <v>17.70557193198582</v>
+        <v>17.98548497129676</v>
       </c>
     </row>
     <row r="493">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="D495">
-        <v>12.96943714885955</v>
+        <v>13.06220685794115</v>
       </c>
     </row>
     <row r="496">
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="D498">
-        <v>12.16941138926549</v>
+        <v>12.42029118732512</v>
       </c>
     </row>
     <row r="499">
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="D504">
-        <v>9.49889785581524</v>
+        <v>9.586750110346362</v>
       </c>
     </row>
     <row r="505">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D507">
-        <v>8.065244700482808</v>
+        <v>8.167607351806183</v>
       </c>
     </row>
     <row r="508">
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="D510">
-        <v>9.897395297632837</v>
+        <v>10.19316461753344</v>
       </c>
     </row>
     <row r="511">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="D513">
-        <v>10.218110263254</v>
+        <v>10.42477291218996</v>
       </c>
     </row>
     <row r="514">
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D519">
-        <v>10.41835668210043</v>
+        <v>10.6039735973753</v>
       </c>
     </row>
     <row r="520">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="D522">
-        <v>12.02640346854916</v>
+        <v>12.36704328429186</v>
       </c>
     </row>
     <row r="523">
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="D528">
-        <v>10.81283672770261</v>
+        <v>10.89291462934903</v>
       </c>
     </row>
     <row r="529">
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="D534">
-        <v>8.639624781724379</v>
+        <v>8.712979892206699</v>
       </c>
     </row>
     <row r="535">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="D537">
-        <v>10.50284793374692</v>
+        <v>10.65672612202676</v>
       </c>
     </row>
     <row r="538">
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="D540">
-        <v>11.52484868635352</v>
+        <v>11.61444304184734</v>
       </c>
     </row>
     <row r="541">
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="D552">
-        <v>11.07376278420784</v>
+        <v>11.14519857355744</v>
       </c>
     </row>
     <row r="553">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="D555">
-        <v>11.33701904348944</v>
+        <v>11.40868421313681</v>
       </c>
     </row>
     <row r="556">
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="D564">
-        <v>10.45896734458771</v>
+        <v>10.51857155257859</v>
       </c>
     </row>
     <row r="565">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="D570">
-        <v>9.123522035509444</v>
+        <v>9.481903016604956</v>
       </c>
     </row>
     <row r="571">
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="D576">
-        <v>10.95357752799289</v>
+        <v>11.48205543670373</v>
       </c>
     </row>
     <row r="577">
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="D579">
-        <v>15.20717333984185</v>
+        <v>15.30593608573874</v>
       </c>
     </row>
     <row r="580">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="D582">
-        <v>14.33858321675414</v>
+        <v>14.47173213607341</v>
       </c>
     </row>
     <row r="583">
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="D585">
-        <v>15.51069736611189</v>
+        <v>15.61822923769451</v>
       </c>
     </row>
     <row r="586">
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="D588">
-        <v>14.09542280858739</v>
+        <v>14.65672493598949</v>
       </c>
     </row>
     <row r="589">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="D591">
-        <v>12.77783505627143</v>
+        <v>13.19772618726942</v>
       </c>
     </row>
     <row r="592">
@@ -11054,7 +11054,7 @@
         </is>
       </c>
       <c r="D594">
-        <v>10</v>
+        <v>10.25470733810751</v>
       </c>
     </row>
     <row r="595">
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="D597">
-        <v>8.759006940765683</v>
+        <v>8.810139045817271</v>
       </c>
     </row>
     <row r="598">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="D603">
-        <v>7.996071069541896</v>
+        <v>8.08934162887299</v>
       </c>
     </row>
     <row r="604">
@@ -11270,7 +11270,7 @@
         </is>
       </c>
       <c r="D606">
-        <v>7.481725450313471</v>
+        <v>7.553131193613686</v>
       </c>
     </row>
     <row r="607">
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="D609">
-        <v>12.71321345966379</v>
+        <v>12.77991296345845</v>
       </c>
     </row>
     <row r="610">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="D612">
-        <v>9.1645997448333</v>
+        <v>9.26722260242857</v>
       </c>
     </row>
     <row r="613">
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="D618">
-        <v>11.06434219652243</v>
+        <v>11.15036045359514</v>
       </c>
     </row>
     <row r="619">
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="D624">
-        <v>10.32784902024128</v>
+        <v>10.50760669534467</v>
       </c>
     </row>
     <row r="625">
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="D627">
-        <v>9.89358449901238</v>
+        <v>10</v>
       </c>
     </row>
     <row r="628">
@@ -11864,7 +11864,7 @@
         </is>
       </c>
       <c r="D639">
-        <v>6.258816775679988</v>
+        <v>6.314935745801502</v>
       </c>
     </row>
     <row r="640">
